--- a/database/event/3603/event_3603_evp_summary.xlsx
+++ b/database/event/3603/event_3603_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>0.7969000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2834</v>
+        <v>3.2097</v>
       </c>
       <c r="E2" t="n">
         <v>9.1707</v>
@@ -548,7 +548,7 @@
         <v>0.7907</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2544</v>
+        <v>3.1811</v>
       </c>
       <c r="E3" t="n">
         <v>9.099</v>
@@ -594,7 +594,7 @@
         <v>0.7396</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0167</v>
+        <v>2.9467</v>
       </c>
       <c r="E4" t="n">
         <v>8.5105</v>
@@ -640,7 +640,7 @@
         <v>0.5108</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9532</v>
+        <v>1.8978</v>
       </c>
       <c r="E5" t="n">
         <v>5.8779</v>
@@ -686,7 +686,7 @@
         <v>0.4852</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8344</v>
+        <v>1.7807</v>
       </c>
       <c r="E6" t="n">
         <v>5.5838</v>
@@ -732,7 +732,7 @@
         <v>0.3337</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1302</v>
+        <v>1.0862</v>
       </c>
       <c r="E7" t="n">
         <v>3.8406</v>
@@ -778,7 +778,7 @@
         <v>0.2164</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5847</v>
+        <v>0.5483</v>
       </c>
       <c r="E8" t="n">
         <v>2.4904</v>
@@ -824,7 +824,7 @@
         <v>0.1968</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4936</v>
+        <v>0.4584</v>
       </c>
       <c r="E9" t="n">
         <v>2.2649</v>
@@ -870,7 +870,7 @@
         <v>0.1892</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4581</v>
+        <v>0.4234</v>
       </c>
       <c r="E10" t="n">
         <v>2.1769</v>
@@ -916,7 +916,7 @@
         <v>0.1562</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3045</v>
+        <v>0.272</v>
       </c>
       <c r="E11" t="n">
         <v>1.7969</v>
@@ -962,7 +962,7 @@
         <v>0.134</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2015</v>
+        <v>0.1703</v>
       </c>
       <c r="E12" t="n">
         <v>1.5417</v>
@@ -1008,7 +1008,7 @@
         <v>0.1284</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1756</v>
+        <v>0.1448</v>
       </c>
       <c r="E13" t="n">
         <v>1.4777</v>
@@ -1054,7 +1054,7 @@
         <v>0.0983</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0357</v>
+        <v>0.0068</v>
       </c>
       <c r="E14" t="n">
         <v>1.1314</v>
@@ -1100,7 +1100,7 @@
         <v>0.096</v>
       </c>
       <c r="D15" t="n">
-        <v>0.025</v>
+        <v>-0.0037</v>
       </c>
       <c r="E15" t="n">
         <v>1.105</v>
@@ -1146,7 +1146,7 @@
         <v>0.0858</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0226</v>
+        <v>-0.0506</v>
       </c>
       <c r="E16" t="n">
         <v>0.9871</v>
@@ -1192,7 +1192,7 @@
         <v>0.0856</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0236</v>
+        <v>-0.0517</v>
       </c>
       <c r="E17" t="n">
         <v>0.9845</v>
@@ -1238,7 +1238,7 @@
         <v>0.0712</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0901</v>
+        <v>-0.1173</v>
       </c>
       <c r="E18" t="n">
         <v>0.8199</v>
@@ -1284,7 +1284,7 @@
         <v>0.0555</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1634</v>
+        <v>-0.1895</v>
       </c>
       <c r="E19" t="n">
         <v>0.6385999999999999</v>
@@ -1330,7 +1330,7 @@
         <v>0.0542</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1695</v>
+        <v>-0.1955</v>
       </c>
       <c r="E20" t="n">
         <v>0.6235000000000001</v>
@@ -1376,7 +1376,7 @@
         <v>0.0162</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3459</v>
+        <v>-0.3694</v>
       </c>
       <c r="E21" t="n">
         <v>0.1869</v>
@@ -1422,7 +1422,7 @@
         <v>0.0009</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4172</v>
+        <v>-0.4398</v>
       </c>
       <c r="E22" t="n">
         <v>0.0103</v>
@@ -1468,7 +1468,7 @@
         <v>-0.0064</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.451</v>
+        <v>-0.4732</v>
       </c>
       <c r="E23" t="n">
         <v>-0.07340000000000001</v>
@@ -1514,7 +1514,7 @@
         <v>-0.007</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4537</v>
+        <v>-0.4758</v>
       </c>
       <c r="E24" t="n">
         <v>-0.0801</v>
@@ -1560,7 +1560,7 @@
         <v>-0.008699999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.462</v>
+        <v>-0.484</v>
       </c>
       <c r="E25" t="n">
         <v>-0.1006</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0201</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.515</v>
+        <v>-0.5363</v>
       </c>
       <c r="E26" t="n">
         <v>-0.2318</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0279</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5512</v>
+        <v>-0.572</v>
       </c>
       <c r="E27" t="n">
         <v>-0.3214</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0283</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.553</v>
+        <v>-0.5737</v>
       </c>
       <c r="E28" t="n">
         <v>-0.3258</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0319</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5696</v>
+        <v>-0.5901</v>
       </c>
       <c r="E29" t="n">
         <v>-0.367</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0477</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6431</v>
+        <v>-0.6626</v>
       </c>
       <c r="E30" t="n">
         <v>-0.5489000000000001</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0609</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7047</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="E31" t="n">
         <v>-0.7013</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0621</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7102000000000001</v>
+        <v>-0.7288</v>
       </c>
       <c r="E32" t="n">
         <v>-0.715</v>
@@ -1928,7 +1928,7 @@
         <v>-0.07190000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7556</v>
+        <v>-0.7735</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8273</v>
@@ -1974,7 +1974,7 @@
         <v>-0.113</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E34" t="n">
         <v>-1.3</v>
@@ -2020,7 +2020,7 @@
         <v>-0.113</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E35" t="n">
         <v>-1.3</v>
@@ -2066,7 +2066,7 @@
         <v>-0.113</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3</v>
@@ -2112,7 +2112,7 @@
         <v>-0.113</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3</v>
@@ -2158,7 +2158,7 @@
         <v>-0.113</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E38" t="n">
         <v>-1.3</v>
@@ -2204,7 +2204,7 @@
         <v>-0.113</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9465</v>
+        <v>-0.9618</v>
       </c>
       <c r="E39" t="n">
         <v>-1.3</v>
@@ -2250,7 +2250,7 @@
         <v>-0.1323</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0362</v>
+        <v>-1.0502</v>
       </c>
       <c r="E40" t="n">
         <v>-1.5219</v>
@@ -2296,7 +2296,7 @@
         <v>-0.1951</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3285</v>
+        <v>-1.3385</v>
       </c>
       <c r="E41" t="n">
         <v>-2.2455</v>

--- a/database/event/3603/event_3603_evp_summary.xlsx
+++ b/database/event/3603/event_3603_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.1707</v>
+        <v>8.7355</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.7591</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2097</v>
+        <v>3.3056</v>
       </c>
       <c r="E2" t="n">
-        <v>9.1707</v>
+        <v>8.7355</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>9.1707</v>
+        <v>8.7355</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>7.0544</v>
+        <v>6.2604</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>7.0544</v>
+        <v>6.2604</v>
       </c>
       <c r="N2" t="n">
         <v>156</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.099</v>
+        <v>8.0923</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7907</v>
+        <v>0.7032</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1811</v>
+        <v>3.0153</v>
       </c>
       <c r="E3" t="n">
-        <v>9.099</v>
+        <v>8.0923</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9.099</v>
+        <v>8.0923</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6.9992</v>
+        <v>5.7994</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>156</v>
       </c>
       <c r="M3" t="n">
-        <v>6.9992</v>
+        <v>5.7994</v>
       </c>
       <c r="N3" t="n">
         <v>156</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.5105</v>
+        <v>7.8896</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7396</v>
+        <v>0.6856</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9467</v>
+        <v>2.9237</v>
       </c>
       <c r="E4" t="n">
-        <v>8.5105</v>
+        <v>7.8896</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>8.5105</v>
+        <v>7.8896</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6.5465</v>
+        <v>5.6542</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>156</v>
       </c>
       <c r="M4" t="n">
-        <v>6.5465</v>
+        <v>5.6542</v>
       </c>
       <c r="N4" t="n">
         <v>156</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.8779</v>
+        <v>5.7736</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5108</v>
+        <v>0.5017</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8978</v>
+        <v>1.9685</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8779</v>
+        <v>5.7736</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5.8779</v>
+        <v>5.7736</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5214</v>
+        <v>4.1377</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>156</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5214</v>
+        <v>4.1377</v>
       </c>
       <c r="N5" t="n">
         <v>156</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.5838</v>
+        <v>4.9829</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4852</v>
+        <v>0.433</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7807</v>
+        <v>1.6115</v>
       </c>
       <c r="E6" t="n">
-        <v>5.5838</v>
+        <v>4.9829</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5.5838</v>
+        <v>4.9829</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2952</v>
+        <v>3.571</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>144</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2952</v>
+        <v>3.571</v>
       </c>
       <c r="N6" t="n">
         <v>144</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8406</v>
+        <v>3.6855</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3337</v>
+        <v>0.3203</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0862</v>
+        <v>1.0258</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8406</v>
+        <v>3.6855</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8406</v>
+        <v>3.6855</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9543</v>
+        <v>2.6412</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>144</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9543</v>
+        <v>2.6412</v>
       </c>
       <c r="N7" t="n">
         <v>144</v>
@@ -768,26 +768,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XigN</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4904</v>
+        <v>2.5336</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2164</v>
+        <v>0.2202</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5483</v>
+        <v>0.5058</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4904</v>
+        <v>2.5336</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4904</v>
+        <v>2.5336</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,44 +796,44 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9157</v>
+        <v>1.8157</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9157</v>
+        <v>1.8157</v>
       </c>
       <c r="N8" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>XigN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2649</v>
+        <v>1.9257</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1968</v>
+        <v>0.1673</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4584</v>
+        <v>0.2313</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2649</v>
+        <v>1.9257</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2649</v>
+        <v>1.9257</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,19 +842,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7422</v>
+        <v>1.3801</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="M9" t="n">
-        <v>1.7422</v>
+        <v>1.3801</v>
       </c>
       <c r="N9" t="n">
-        <v>156</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1769</v>
+        <v>1.8914</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1892</v>
+        <v>0.1644</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4234</v>
+        <v>0.2159</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1769</v>
+        <v>1.8914</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1769</v>
+        <v>1.8914</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6745</v>
+        <v>1.3555</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>144</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6745</v>
+        <v>1.3555</v>
       </c>
       <c r="N10" t="n">
         <v>144</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.7969</v>
+        <v>1.5921</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1562</v>
+        <v>0.1384</v>
       </c>
       <c r="D11" t="n">
-        <v>0.272</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7969</v>
+        <v>1.5921</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7969</v>
+        <v>1.5921</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3822</v>
+        <v>1.141</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>77</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3822</v>
+        <v>1.141</v>
       </c>
       <c r="N11" t="n">
         <v>77</v>
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5417</v>
+        <v>1.5218</v>
       </c>
       <c r="C12" t="n">
-        <v>0.134</v>
+        <v>0.1322</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1703</v>
+        <v>0.049</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5417</v>
+        <v>1.5218</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5417</v>
+        <v>1.5218</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1859</v>
+        <v>1.0906</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>233</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1859</v>
+        <v>1.0906</v>
       </c>
       <c r="N12" t="n">
         <v>233</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4777</v>
+        <v>1.4816</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1284</v>
+        <v>0.1288</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1448</v>
+        <v>0.0309</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4777</v>
+        <v>1.4816</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4777</v>
+        <v>1.4816</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1367</v>
+        <v>1.0618</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>233</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1367</v>
+        <v>1.0618</v>
       </c>
       <c r="N13" t="n">
         <v>233</v>
@@ -1044,26 +1044,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1314</v>
+        <v>1.0966</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0983</v>
+        <v>0.0953</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0068</v>
+        <v>-0.143</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1314</v>
+        <v>1.0966</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1314</v>
+        <v>1.0966</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,44 +1072,44 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8703</v>
+        <v>0.7859</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>233</v>
+        <v>85</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8703</v>
+        <v>0.7859</v>
       </c>
       <c r="N14" t="n">
-        <v>233</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.105</v>
+        <v>1.0677</v>
       </c>
       <c r="C15" t="n">
-        <v>0.096</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0037</v>
+        <v>-0.156</v>
       </c>
       <c r="E15" t="n">
-        <v>1.105</v>
+        <v>1.0677</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.105</v>
+        <v>1.0677</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.85</v>
+        <v>0.7652</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>85</v>
+        <v>233</v>
       </c>
       <c r="M15" t="n">
-        <v>0.85</v>
+        <v>0.7652</v>
       </c>
       <c r="N15" t="n">
-        <v>85</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MINISE</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9871</v>
+        <v>0.9134</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0858</v>
+        <v>0.0794</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0506</v>
+        <v>-0.2257</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9871</v>
+        <v>0.9134</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9871</v>
+        <v>0.9134</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7593</v>
+        <v>0.6546</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7593</v>
+        <v>0.6546</v>
       </c>
       <c r="N16" t="n">
-        <v>233</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>MINISE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9845</v>
+        <v>0.8953</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0856</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0517</v>
+        <v>-0.2338</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9845</v>
+        <v>0.8953</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9845</v>
+        <v>0.8953</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,44 +1210,44 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7573</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7573</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>77</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8199</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0712</v>
+        <v>0.067</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1173</v>
+        <v>-0.2901</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8199</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8199</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6307</v>
+        <v>0.5523</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>77</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6307</v>
+        <v>0.5523</v>
       </c>
       <c r="N18" t="n">
         <v>77</v>
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0555</v>
+        <v>0.065</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1895</v>
+        <v>-0.3001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4912</v>
+        <v>0.5364</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>77</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4912</v>
+        <v>0.5364</v>
       </c>
       <c r="N19" t="n">
         <v>77</v>
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.5089</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0542</v>
+        <v>0.0442</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1955</v>
+        <v>-0.4083</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.5089</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.5089</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4796</v>
+        <v>0.3647</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>85</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4796</v>
+        <v>0.3647</v>
       </c>
       <c r="N20" t="n">
         <v>85</v>
@@ -1366,26 +1366,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Subroza</t>
+          <t>xeta</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1869</v>
+        <v>0.2577</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0162</v>
+        <v>0.0224</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3694</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1869</v>
+        <v>0.2577</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1869</v>
+        <v>0.2577</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,44 +1394,44 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1438</v>
+        <v>0.1847</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1438</v>
+        <v>0.1847</v>
       </c>
       <c r="N21" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Subroza</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0103</v>
+        <v>0.242</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0009</v>
+        <v>0.021</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4398</v>
+        <v>-0.5288</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0103</v>
+        <v>0.242</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0103</v>
+        <v>0.242</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,44 +1440,44 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.1734</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="M22" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.1734</v>
       </c>
       <c r="N22" t="n">
-        <v>65</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>reatz</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.07340000000000001</v>
+        <v>0.0363</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0064</v>
+        <v>0.0032</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4732</v>
+        <v>-0.6216</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.07340000000000001</v>
+        <v>0.0363</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.07340000000000001</v>
+        <v>0.0363</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,44 +1486,44 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0565</v>
+        <v>0.026</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0565</v>
+        <v>0.026</v>
       </c>
       <c r="N23" t="n">
-        <v>233</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.0801</v>
+        <v>0.0022</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.007</v>
+        <v>0.0002</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4758</v>
+        <v>-0.637</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0801</v>
+        <v>0.0022</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0801</v>
+        <v>0.0022</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,44 +1532,44 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0616</v>
+        <v>0.0016</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0616</v>
+        <v>0.0016</v>
       </c>
       <c r="N24" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>xeta</t>
+          <t>solo</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1006</v>
+        <v>-0.0007</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.484</v>
+        <v>-0.6383</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1006</v>
+        <v>-0.0007</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1006</v>
+        <v>-0.0007</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0774</v>
+        <v>-0.0005</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>128</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0774</v>
+        <v>-0.0005</v>
       </c>
       <c r="N25" t="n">
         <v>128</v>
@@ -1596,26 +1596,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2318</v>
+        <v>-0.1058</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0201</v>
+        <v>-0.0092</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5363</v>
+        <v>-0.6858</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2318</v>
+        <v>-0.1058</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2318</v>
+        <v>-0.1058</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,44 +1624,44 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1783</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1783</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>solo</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3214</v>
+        <v>-0.1436</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0279</v>
+        <v>-0.0125</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.572</v>
+        <v>-0.7028</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3214</v>
+        <v>-0.1436</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3214</v>
+        <v>-0.1436</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,44 +1670,44 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2472</v>
+        <v>-0.1029</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2472</v>
+        <v>-0.1029</v>
       </c>
       <c r="N27" t="n">
-        <v>128</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>reatz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3258</v>
+        <v>-0.1956</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0283</v>
+        <v>-0.017</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5737</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3258</v>
+        <v>-0.1956</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.3258</v>
+        <v>-0.1956</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.2506</v>
+        <v>-0.1402</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2506</v>
+        <v>-0.1402</v>
       </c>
       <c r="N28" t="n">
-        <v>77</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>xccurate</t>
+          <t>zeff</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.367</v>
+        <v>-0.2605</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0319</v>
+        <v>-0.0226</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5901</v>
+        <v>-0.7556</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.367</v>
+        <v>-0.2605</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.367</v>
+        <v>-0.2605</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,44 +1762,44 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2823</v>
+        <v>-0.1867</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2823</v>
+        <v>-0.1867</v>
       </c>
       <c r="N29" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>xccurate</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.2782</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0477</v>
+        <v>-0.0242</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6626</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.2782</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.2782</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,44 +1808,44 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4222</v>
+        <v>-0.1994</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4222</v>
+        <v>-0.1994</v>
       </c>
       <c r="N30" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>zeff</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7013</v>
+        <v>-0.4165</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0609</v>
+        <v>-0.0362</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.826</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7013</v>
+        <v>-0.4165</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.7013</v>
+        <v>-0.4165</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,19 +1854,19 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5395</v>
+        <v>-0.2985</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5395</v>
+        <v>-0.2985</v>
       </c>
       <c r="N31" t="n">
-        <v>128</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32">
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.715</v>
+        <v>-0.4563</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0621</v>
+        <v>-0.0397</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7288</v>
+        <v>-0.844</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.715</v>
+        <v>-0.4563</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.715</v>
+        <v>-0.4563</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.55</v>
+        <v>-0.327</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>65</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.55</v>
+        <v>-0.327</v>
       </c>
       <c r="N32" t="n">
         <v>65</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8273</v>
+        <v>-0.5329</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0463</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7735</v>
+        <v>-0.8786</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8273</v>
+        <v>-0.5329</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.8273</v>
+        <v>-0.5329</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.6364</v>
+        <v>-0.3819</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>65</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6364</v>
+        <v>-0.3819</v>
       </c>
       <c r="N33" t="n">
         <v>65</v>
@@ -1964,26 +1964,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LOVEYY</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.3</v>
+        <v>-1.0896</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.113</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9618</v>
+        <v>-1.1299</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.3</v>
+        <v>-1.0896</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.3</v>
+        <v>-1.0896</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>-0.7809</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>36</v>
       </c>
       <c r="M34" t="n">
-        <v>-1</v>
+        <v>-0.7809</v>
       </c>
       <c r="N34" t="n">
         <v>36</v>
@@ -2010,26 +2010,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.3</v>
+        <v>-1.1556</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.113</v>
+        <v>-0.1004</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9618</v>
+        <v>-1.1597</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.3</v>
+        <v>-1.1556</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.3</v>
+        <v>-1.1556</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,44 +2038,44 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>-0.8282</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="M35" t="n">
-        <v>-1</v>
+        <v>-0.8282</v>
       </c>
       <c r="N35" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LOVEYY</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3</v>
+        <v>-1.1674</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.113</v>
+        <v>-0.1014</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9618</v>
+        <v>-1.165</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3</v>
+        <v>-1.1674</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.3</v>
+        <v>-1.1674</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,44 +2084,44 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-1</v>
+        <v>-0.8366</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="M36" t="n">
-        <v>-1</v>
+        <v>-0.8366</v>
       </c>
       <c r="N36" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>captainMo</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3</v>
+        <v>-1.2968</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.113</v>
+        <v>-0.1127</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9618</v>
+        <v>-1.2235</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3</v>
+        <v>-1.2968</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.3</v>
+        <v>-1.2968</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,19 +2130,19 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-1</v>
+        <v>-0.9294</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="M37" t="n">
-        <v>-1</v>
+        <v>-0.9294</v>
       </c>
       <c r="N37" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38">
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3</v>
+        <v>-1.3954</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.113</v>
+        <v>-0.1213</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9618</v>
+        <v>-1.268</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3</v>
+        <v>-1.3954</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.3</v>
+        <v>-1.3954</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2194,26 +2194,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>captainMo</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3</v>
+        <v>-1.3954</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.113</v>
+        <v>-0.1213</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9618</v>
+        <v>-1.268</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3</v>
+        <v>-1.3954</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.3</v>
+        <v>-1.3954</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2228,13 +2228,13 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="M39" t="n">
         <v>-1</v>
       </c>
       <c r="N39" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5219</v>
+        <v>-1.4526</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1323</v>
+        <v>-0.1262</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0502</v>
+        <v>-1.2938</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5219</v>
+        <v>-1.4526</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.5219</v>
+        <v>-1.4526</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.1707</v>
+        <v>-1.041</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>128</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1707</v>
+        <v>-1.041</v>
       </c>
       <c r="N40" t="n">
         <v>128</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.2455</v>
+        <v>-1.6982</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1951</v>
+        <v>-0.1476</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3385</v>
+        <v>-1.4047</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.2455</v>
+        <v>-1.6982</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.2455</v>
+        <v>-1.6982</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.7273</v>
+        <v>-1.217</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>144</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7273</v>
+        <v>-1.217</v>
       </c>
       <c r="N41" t="n">
         <v>144</v>
@@ -2429,10 +2429,10 @@
         <v>0.7</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3388</v>
+        <v>-0.2776</v>
       </c>
       <c r="J2" t="n">
-        <v>-7.4536</v>
+        <v>-6.1072</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3544</v>
+        <v>-0.2878</v>
       </c>
       <c r="J3" t="n">
-        <v>-7.7968</v>
+        <v>-6.3316</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.63</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4505</v>
+        <v>-0.3464</v>
       </c>
       <c r="J4" t="n">
-        <v>-9.911</v>
+        <v>-7.6208</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5855</v>
+        <v>-0.4085</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.881</v>
+        <v>-8.987</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.4</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8134</v>
+        <v>-0.5592</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.8948</v>
+        <v>-12.3024</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.65</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3785</v>
+        <v>1.2682</v>
       </c>
       <c r="J7" t="n">
-        <v>30.327</v>
+        <v>27.9004</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.62</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3204</v>
+        <v>1.2335</v>
       </c>
       <c r="J8" t="n">
-        <v>29.0488</v>
+        <v>27.137</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2809</v>
+        <v>1.2103</v>
       </c>
       <c r="J9" t="n">
-        <v>28.1798</v>
+        <v>26.6266</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.49</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0347</v>
+        <v>1.0829</v>
       </c>
       <c r="J10" t="n">
-        <v>22.7634</v>
+        <v>23.8238</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1661</v>
+        <v>0.2652</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6542</v>
+        <v>5.8344</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.34</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5616</v>
+        <v>0.6745</v>
       </c>
       <c r="J12" t="n">
-        <v>16.848</v>
+        <v>20.235</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3136</v>
+        <v>0.3557</v>
       </c>
       <c r="J13" t="n">
-        <v>9.407999999999999</v>
+        <v>10.671</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0435</v>
+        <v>0.0626</v>
       </c>
       <c r="J14" t="n">
-        <v>1.305</v>
+        <v>1.878</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2368</v>
+        <v>-0.1376</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.104</v>
+        <v>-4.128</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.73</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4863</v>
+        <v>-0.311</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.589</v>
+        <v>-9.33</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.19</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6019</v>
+        <v>0.5689</v>
       </c>
       <c r="J17" t="n">
-        <v>18.057</v>
+        <v>17.067</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.19</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6019</v>
+        <v>0.5689</v>
       </c>
       <c r="J18" t="n">
-        <v>18.057</v>
+        <v>17.067</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.17</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5495</v>
+        <v>0.5174</v>
       </c>
       <c r="J19" t="n">
-        <v>16.485</v>
+        <v>15.522</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.05</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1619</v>
+        <v>0.1839</v>
       </c>
       <c r="J20" t="n">
-        <v>4.857</v>
+        <v>5.517</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.73</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8569</v>
+        <v>-0.8181</v>
       </c>
       <c r="J21" t="n">
-        <v>-25.707</v>
+        <v>-24.543</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.77</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.19</v>
+        <v>-0.1752</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.23</v>
+        <v>-2.9784</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.74</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2362</v>
+        <v>-0.2098</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.0154</v>
+        <v>-3.5666</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.67</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.343</v>
+        <v>-0.2869</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.831</v>
+        <v>-4.8773</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.25</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9889</v>
+        <v>-0.6937</v>
       </c>
       <c r="J25" t="n">
-        <v>-16.8113</v>
+        <v>-11.7929</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.21</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.0387</v>
+        <v>-0.7338</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.6579</v>
+        <v>-12.4746</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>2.63</v>
       </c>
       <c r="I27" t="n">
-        <v>2.3259</v>
+        <v>1.8681</v>
       </c>
       <c r="J27" t="n">
-        <v>39.5403</v>
+        <v>31.7577</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.68</v>
       </c>
       <c r="I28" t="n">
-        <v>1.358</v>
+        <v>1.2844</v>
       </c>
       <c r="J28" t="n">
-        <v>23.086</v>
+        <v>21.8348</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.49</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9560999999999999</v>
+        <v>1.0681</v>
       </c>
       <c r="J29" t="n">
-        <v>16.2537</v>
+        <v>18.1577</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.31</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5905</v>
+        <v>0.7294</v>
       </c>
       <c r="J30" t="n">
-        <v>10.0385</v>
+        <v>12.3998</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.16</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2571</v>
+        <v>0.3689</v>
       </c>
       <c r="J31" t="n">
-        <v>4.3707</v>
+        <v>6.2713</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.05</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2005</v>
+        <v>0.1884</v>
       </c>
       <c r="J32" t="n">
-        <v>5.0125</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1126</v>
+        <v>0.0804</v>
       </c>
       <c r="J33" t="n">
-        <v>2.815</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.85</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2327</v>
+        <v>-0.1708</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.8175</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.74</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4253</v>
+        <v>-0.2778</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.6325</v>
+        <v>-6.945</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.55</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6805</v>
+        <v>-0.4566</v>
       </c>
       <c r="J36" t="n">
-        <v>-17.0125</v>
+        <v>-11.415</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.907</v>
+        <v>0.6781</v>
       </c>
       <c r="J37" t="n">
-        <v>22.675</v>
+        <v>16.9525</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.35</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8845</v>
+        <v>0.665</v>
       </c>
       <c r="J38" t="n">
-        <v>22.1125</v>
+        <v>16.625</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.29</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7432</v>
+        <v>0.5854</v>
       </c>
       <c r="J39" t="n">
-        <v>18.58</v>
+        <v>14.635</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.22</v>
       </c>
       <c r="I40" t="n">
-        <v>0.5435</v>
+        <v>0.4916</v>
       </c>
       <c r="J40" t="n">
-        <v>13.5875</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.98</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.237</v>
+        <v>-0.1546</v>
       </c>
       <c r="J41" t="n">
-        <v>-5.925</v>
+        <v>-3.865</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.26</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4975</v>
+        <v>0.4803</v>
       </c>
       <c r="J42" t="n">
-        <v>12.935</v>
+        <v>12.4878</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.09</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2437</v>
+        <v>0.2509</v>
       </c>
       <c r="J43" t="n">
-        <v>6.3362</v>
+        <v>6.5234</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.92</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.144</v>
+        <v>-0.1038</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.744</v>
+        <v>-2.6988</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.87</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2473</v>
+        <v>-0.1571</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.4298</v>
+        <v>-4.0846</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.43</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.834</v>
+        <v>-0.5737</v>
       </c>
       <c r="J46" t="n">
-        <v>-21.684</v>
+        <v>-14.9162</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.46</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1341</v>
+        <v>0.8131</v>
       </c>
       <c r="J47" t="n">
-        <v>29.4866</v>
+        <v>21.1406</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8763</v>
+        <v>0.6561</v>
       </c>
       <c r="J48" t="n">
-        <v>22.7838</v>
+        <v>17.0586</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.27</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7108</v>
+        <v>0.5619</v>
       </c>
       <c r="J49" t="n">
-        <v>18.4808</v>
+        <v>14.6094</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.02</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0281</v>
+        <v>0.0439</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.7306</v>
+        <v>1.1414</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.98</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2285</v>
+        <v>-0.1482</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.941</v>
+        <v>-3.8532</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2051</v>
+        <v>0.8537</v>
       </c>
       <c r="J52" t="n">
-        <v>36.153</v>
+        <v>25.611</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.699</v>
+        <v>0.5433</v>
       </c>
       <c r="J53" t="n">
-        <v>20.97</v>
+        <v>16.299</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.24</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6743</v>
+        <v>0.5292</v>
       </c>
       <c r="J54" t="n">
-        <v>20.229</v>
+        <v>15.876</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.12</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3219</v>
+        <v>0.3539</v>
       </c>
       <c r="J55" t="n">
-        <v>9.657</v>
+        <v>10.617</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.989</v>
+        <v>-0.9625</v>
       </c>
       <c r="J56" t="n">
-        <v>-29.67</v>
+        <v>-28.875</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.31</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5292</v>
+        <v>0.5084</v>
       </c>
       <c r="J57" t="n">
-        <v>15.876</v>
+        <v>15.252</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.408</v>
+        <v>0.4149</v>
       </c>
       <c r="J58" t="n">
-        <v>12.24</v>
+        <v>12.447</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.02</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0605</v>
+        <v>0.0644</v>
       </c>
       <c r="J59" t="n">
-        <v>1.815</v>
+        <v>1.932</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3863</v>
+        <v>-0.2404</v>
       </c>
       <c r="J60" t="n">
-        <v>-11.589</v>
+        <v>-7.212</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5094</v>
+        <v>-0.3281</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.282</v>
+        <v>-9.843</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.13</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3577</v>
+        <v>0.2994</v>
       </c>
       <c r="J62" t="n">
-        <v>8.942500000000001</v>
+        <v>7.485</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.75</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3899</v>
+        <v>-0.2619</v>
       </c>
       <c r="J63" t="n">
-        <v>-9.7475</v>
+        <v>-6.5475</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.73</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4215</v>
+        <v>-0.2809</v>
       </c>
       <c r="J64" t="n">
-        <v>-10.5375</v>
+        <v>-7.0225</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.68</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4958</v>
+        <v>-0.3283</v>
       </c>
       <c r="J65" t="n">
-        <v>-12.395</v>
+        <v>-8.2075</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.67</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.51</v>
+        <v>-0.3378</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.75</v>
+        <v>-8.445</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8678</v>
+        <v>0.6009</v>
       </c>
       <c r="J67" t="n">
-        <v>21.695</v>
+        <v>15.0225</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.56</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7479</v>
+        <v>0.5331</v>
       </c>
       <c r="J68" t="n">
-        <v>18.6975</v>
+        <v>13.3275</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.27</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3714</v>
+        <v>0.347</v>
       </c>
       <c r="J69" t="n">
-        <v>9.285</v>
+        <v>8.675000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0264</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.1625</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.91</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2707</v>
+        <v>-0.1516</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.7675</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.52</v>
       </c>
       <c r="I72" t="n">
-        <v>1.281</v>
+        <v>0.9033</v>
       </c>
       <c r="J72" t="n">
-        <v>30.744</v>
+        <v>21.6792</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>1.0565</v>
+        <v>0.7597</v>
       </c>
       <c r="J73" t="n">
-        <v>25.356</v>
+        <v>18.2328</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.13</v>
       </c>
       <c r="I74" t="n">
-        <v>0.346</v>
+        <v>0.3686</v>
       </c>
       <c r="J74" t="n">
-        <v>8.304</v>
+        <v>8.846399999999999</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.88</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.5189</v>
+        <v>-0.4509</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.4536</v>
+        <v>-10.8216</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.87</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5455</v>
+        <v>-0.4788</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.092</v>
+        <v>-11.4912</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4145</v>
+        <v>0.4214</v>
       </c>
       <c r="J77" t="n">
-        <v>9.948</v>
+        <v>10.1136</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3274</v>
+        <v>0.3572</v>
       </c>
       <c r="J78" t="n">
-        <v>7.8576</v>
+        <v>8.572800000000001</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.01</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0139</v>
+        <v>0.0337</v>
       </c>
       <c r="J79" t="n">
-        <v>0.3336</v>
+        <v>0.8088</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2545</v>
+        <v>-0.1491</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.108</v>
+        <v>-3.5784</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2867</v>
+        <v>-0.1707</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.8808</v>
+        <v>-4.0968</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.96</v>
       </c>
       <c r="I82" t="n">
-        <v>1.8338</v>
+        <v>1.344</v>
       </c>
       <c r="J82" t="n">
-        <v>34.8422</v>
+        <v>25.536</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.88</v>
       </c>
       <c r="I83" t="n">
-        <v>1.7578</v>
+        <v>1.2547</v>
       </c>
       <c r="J83" t="n">
-        <v>33.3982</v>
+        <v>23.8393</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.75</v>
       </c>
       <c r="I84" t="n">
-        <v>1.5603</v>
+        <v>1.1077</v>
       </c>
       <c r="J84" t="n">
-        <v>29.6457</v>
+        <v>21.0463</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2038</v>
+        <v>-0.1157</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.8722</v>
+        <v>-2.1983</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.93</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.461</v>
+        <v>-0.3793</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.759</v>
+        <v>-7.2067</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.96</v>
       </c>
       <c r="I87" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0716</v>
       </c>
       <c r="J87" t="n">
-        <v>1.8449</v>
+        <v>1.3604</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.58</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.5417</v>
+        <v>-0.3891</v>
       </c>
       <c r="J88" t="n">
-        <v>-10.2923</v>
+        <v>-7.3929</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.54</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.6115</v>
+        <v>-0.425</v>
       </c>
       <c r="J89" t="n">
-        <v>-11.6185</v>
+        <v>-8.074999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.47</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.7153</v>
+        <v>-0.4905</v>
       </c>
       <c r="J90" t="n">
-        <v>-13.5907</v>
+        <v>-9.3195</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.38</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8367</v>
+        <v>-0.5766</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.8973</v>
+        <v>-10.9554</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>2.12</v>
       </c>
       <c r="I92" t="n">
-        <v>1.9408</v>
+        <v>1.4823</v>
       </c>
       <c r="J92" t="n">
-        <v>32.9936</v>
+        <v>25.1991</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.88</v>
       </c>
       <c r="I93" t="n">
-        <v>1.7088</v>
+        <v>1.2254</v>
       </c>
       <c r="J93" t="n">
-        <v>29.0496</v>
+        <v>20.8318</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.57</v>
       </c>
       <c r="I94" t="n">
-        <v>1.1026</v>
+        <v>0.8857</v>
       </c>
       <c r="J94" t="n">
-        <v>18.7442</v>
+        <v>15.0569</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.5</v>
       </c>
       <c r="I95" t="n">
-        <v>0.9655</v>
+        <v>0.8032</v>
       </c>
       <c r="J95" t="n">
-        <v>16.4135</v>
+        <v>13.6544</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.36</v>
       </c>
       <c r="I96" t="n">
-        <v>0.6863</v>
+        <v>0.6291</v>
       </c>
       <c r="J96" t="n">
-        <v>11.6671</v>
+        <v>10.6947</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>0.76</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.1587</v>
+        <v>-0.1474</v>
       </c>
       <c r="J97" t="n">
-        <v>-2.6979</v>
+        <v>-2.5058</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.58</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.4343</v>
+        <v>-0.3559</v>
       </c>
       <c r="J98" t="n">
-        <v>-7.3831</v>
+        <v>-6.0503</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.49</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.5807</v>
+        <v>-0.4475</v>
       </c>
       <c r="J99" t="n">
-        <v>-9.8719</v>
+        <v>-7.6075</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.24</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.9865</v>
+        <v>-0.6915</v>
       </c>
       <c r="J100" t="n">
-        <v>-16.7705</v>
+        <v>-11.7555</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.23</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.9997</v>
+        <v>-0.7019</v>
       </c>
       <c r="J101" t="n">
-        <v>-16.9949</v>
+        <v>-11.9323</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4946</v>
+        <v>0.4852</v>
       </c>
       <c r="J102" t="n">
-        <v>14.3434</v>
+        <v>14.0708</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.23</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3996</v>
+        <v>0.4142</v>
       </c>
       <c r="J103" t="n">
-        <v>11.5884</v>
+        <v>12.0118</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.0042</v>
+        <v>0.0264</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.1218</v>
+        <v>0.7655999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0735</v>
+        <v>-0.0277</v>
       </c>
       <c r="J105" t="n">
-        <v>-2.1315</v>
+        <v>-0.8033</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.86</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3124</v>
+        <v>-0.1862</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.0596</v>
+        <v>-5.3998</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.2</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6445</v>
+        <v>0.4937</v>
       </c>
       <c r="J107" t="n">
-        <v>18.6905</v>
+        <v>14.3173</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.17</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5672</v>
+        <v>0.4478</v>
       </c>
       <c r="J108" t="n">
-        <v>16.4488</v>
+        <v>12.9862</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.05</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2018</v>
+        <v>0.1881</v>
       </c>
       <c r="J109" t="n">
-        <v>5.8522</v>
+        <v>5.4549</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0674</v>
+        <v>0.0871</v>
       </c>
       <c r="J110" t="n">
-        <v>1.9546</v>
+        <v>2.5259</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.75</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.8022</v>
+        <v>-0.7603</v>
       </c>
       <c r="J111" t="n">
-        <v>-23.2638</v>
+        <v>-22.0487</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.88</v>
       </c>
       <c r="I112" t="n">
-        <v>1.029</v>
+        <v>0.6994</v>
       </c>
       <c r="J112" t="n">
-        <v>21.609</v>
+        <v>14.6874</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.84</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9892</v>
+        <v>0.6768</v>
       </c>
       <c r="J113" t="n">
-        <v>20.7732</v>
+        <v>14.2128</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.52</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.4922</v>
       </c>
       <c r="J114" t="n">
-        <v>13.3686</v>
+        <v>10.3362</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.28</v>
       </c>
       <c r="I115" t="n">
-        <v>0.326</v>
+        <v>0.3403</v>
       </c>
       <c r="J115" t="n">
-        <v>6.846</v>
+        <v>7.1463</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.99</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.1497</v>
+        <v>-0.0654</v>
       </c>
       <c r="J116" t="n">
-        <v>-3.1437</v>
+        <v>-1.3734</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5056</v>
+        <v>0.413</v>
       </c>
       <c r="J117" t="n">
-        <v>10.6176</v>
+        <v>8.673</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.78</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2554</v>
+        <v>-0.2141</v>
       </c>
       <c r="J118" t="n">
-        <v>-5.3634</v>
+        <v>-4.4961</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.58</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.5928</v>
+        <v>-0.4028</v>
       </c>
       <c r="J119" t="n">
-        <v>-12.4488</v>
+        <v>-8.4588</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.42</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.8067</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J120" t="n">
-        <v>-16.9407</v>
+        <v>-11.6109</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.38</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.8563</v>
+        <v>-0.5905</v>
       </c>
       <c r="J121" t="n">
-        <v>-17.9823</v>
+        <v>-12.4005</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.44</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7054</v>
+        <v>0.6504</v>
       </c>
       <c r="J122" t="n">
-        <v>19.0458</v>
+        <v>17.5608</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.06</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1694</v>
+        <v>0.1697</v>
       </c>
       <c r="J123" t="n">
-        <v>4.5738</v>
+        <v>4.5819</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.91</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1982</v>
+        <v>-0.1194</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.3514</v>
+        <v>-3.2238</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.71</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.3228</v>
       </c>
       <c r="J125" t="n">
-        <v>-13.5135</v>
+        <v>-8.7156</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.71</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.3228</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.5135</v>
+        <v>-8.7156</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.65</v>
       </c>
       <c r="I127" t="n">
-        <v>1.5143</v>
+        <v>1.0587</v>
       </c>
       <c r="J127" t="n">
-        <v>40.8861</v>
+        <v>28.5849</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.17</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4387</v>
+        <v>0.4253</v>
       </c>
       <c r="J128" t="n">
-        <v>11.8449</v>
+        <v>11.4831</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.08</v>
       </c>
       <c r="I129" t="n">
-        <v>0.18</v>
+        <v>0.2463</v>
       </c>
       <c r="J129" t="n">
-        <v>4.86</v>
+        <v>6.6501</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.04</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0525</v>
+        <v>0.1207</v>
       </c>
       <c r="J130" t="n">
-        <v>1.4175</v>
+        <v>3.2589</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.03</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0173</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>0.4671</v>
+        <v>2.322</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.92</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0852</v>
+        <v>-0.0877</v>
       </c>
       <c r="J132" t="n">
-        <v>-2.0448</v>
+        <v>-2.1048</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.9</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1212</v>
+        <v>-0.1112</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.9088</v>
+        <v>-2.6688</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2802</v>
+        <v>-0.2062</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.7248</v>
+        <v>-4.9488</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.7</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4697</v>
+        <v>-0.3105</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.2728</v>
+        <v>-7.452</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.67</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.339</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.3024</v>
+        <v>-8.135999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.95</v>
       </c>
       <c r="I137" t="n">
-        <v>1.865</v>
+        <v>1.3782</v>
       </c>
       <c r="J137" t="n">
-        <v>44.76</v>
+        <v>33.0768</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.94</v>
       </c>
       <c r="I138" t="n">
-        <v>1.8557</v>
+        <v>1.3666</v>
       </c>
       <c r="J138" t="n">
-        <v>44.5368</v>
+        <v>32.7984</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1858</v>
+        <v>0.2731</v>
       </c>
       <c r="J139" t="n">
-        <v>4.4592</v>
+        <v>6.5544</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6375</v>
+        <v>-0.5718</v>
       </c>
       <c r="J140" t="n">
-        <v>-15.3</v>
+        <v>-13.7232</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.78</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>-18.72</v>
+        <v>-17.4792</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.47</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6528</v>
+        <v>0.4796</v>
       </c>
       <c r="J142" t="n">
-        <v>15.0144</v>
+        <v>11.0308</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.4</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5681</v>
+        <v>0.4344</v>
       </c>
       <c r="J143" t="n">
-        <v>13.0663</v>
+        <v>9.991199999999999</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.15</v>
       </c>
       <c r="I144" t="n">
-        <v>0.201</v>
+        <v>0.2141</v>
       </c>
       <c r="J144" t="n">
-        <v>4.623</v>
+        <v>4.9243</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.14</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1856</v>
+        <v>0.2009</v>
       </c>
       <c r="J145" t="n">
-        <v>4.2688</v>
+        <v>4.6207</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1224</v>
+        <v>0.146</v>
       </c>
       <c r="J146" t="n">
-        <v>2.8152</v>
+        <v>3.358</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.92</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0989</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>-2.2747</v>
+        <v>-2.1436</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.92</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0989</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.2747</v>
+        <v>-2.1436</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.91</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1173</v>
+        <v>-0.1049</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.6979</v>
+        <v>-2.4127</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.78</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3596</v>
+        <v>-0.2378</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.270799999999999</v>
+        <v>-5.4694</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.62</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5889</v>
+        <v>-0.3903</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.5447</v>
+        <v>-8.976900000000001</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.92</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0293</v>
+        <v>-0.0567</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.5274</v>
+        <v>-1.0206</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.77</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2767</v>
+        <v>-0.2268</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.9806</v>
+        <v>-4.0824</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.74</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3248</v>
+        <v>-0.257</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.8464</v>
+        <v>-4.626</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.67</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4554</v>
+        <v>-0.3217</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.1972</v>
+        <v>-5.7906</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.3</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.9538</v>
+        <v>-0.6669</v>
       </c>
       <c r="J156" t="n">
-        <v>-17.1684</v>
+        <v>-12.0042</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.71</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5159</v>
+        <v>1.0735</v>
       </c>
       <c r="J157" t="n">
-        <v>27.2862</v>
+        <v>19.323</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.66</v>
       </c>
       <c r="I158" t="n">
-        <v>1.423</v>
+        <v>1.0152</v>
       </c>
       <c r="J158" t="n">
-        <v>25.614</v>
+        <v>18.2736</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.39</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8376</v>
+        <v>0.6944</v>
       </c>
       <c r="J159" t="n">
-        <v>15.0768</v>
+        <v>12.4992</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.35</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7471</v>
+        <v>0.6438</v>
       </c>
       <c r="J160" t="n">
-        <v>13.4478</v>
+        <v>11.5884</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.07</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0699</v>
+        <v>0.161</v>
       </c>
       <c r="J161" t="n">
-        <v>1.2582</v>
+        <v>2.898</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.37</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6005</v>
+        <v>0.4421</v>
       </c>
       <c r="J162" t="n">
-        <v>18.015</v>
+        <v>13.263</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.16</v>
       </c>
       <c r="I163" t="n">
-        <v>0.315</v>
+        <v>0.254</v>
       </c>
       <c r="J163" t="n">
-        <v>9.449999999999999</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.98</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.0383</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.406</v>
+        <v>-1.149</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.89</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2523</v>
+        <v>-0.1482</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.569</v>
+        <v>-4.446</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.73</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4855</v>
+        <v>-0.3105</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.565</v>
+        <v>-9.315</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.63</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8901</v>
+        <v>0.6479</v>
       </c>
       <c r="J167" t="n">
-        <v>26.703</v>
+        <v>19.437</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.18</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3346</v>
+        <v>0.2954</v>
       </c>
       <c r="J168" t="n">
-        <v>10.038</v>
+        <v>8.862</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.16</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3041</v>
+        <v>0.2673</v>
       </c>
       <c r="J169" t="n">
-        <v>9.122999999999999</v>
+        <v>8.019</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5039</v>
+        <v>-0.3233</v>
       </c>
       <c r="J170" t="n">
-        <v>-15.117</v>
+        <v>-9.699</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.59</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6653</v>
+        <v>-0.4438</v>
       </c>
       <c r="J171" t="n">
-        <v>-19.959</v>
+        <v>-13.314</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.04</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1253</v>
+        <v>0.121</v>
       </c>
       <c r="J172" t="n">
-        <v>3.759</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.04</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1253</v>
+        <v>0.121</v>
       </c>
       <c r="J173" t="n">
-        <v>3.759</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0179</v>
+        <v>0.0032</v>
       </c>
       <c r="J174" t="n">
-        <v>0.537</v>
+        <v>0.096</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1245</v>
+        <v>-0.0736</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.735</v>
+        <v>-2.208</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.85</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3023</v>
+        <v>-0.1852</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.069000000000001</v>
+        <v>-5.556</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.45</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1388</v>
+        <v>0.8119</v>
       </c>
       <c r="J177" t="n">
-        <v>34.164</v>
+        <v>24.357</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.38</v>
       </c>
       <c r="I178" t="n">
-        <v>0.9913</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>29.739</v>
+        <v>21.579</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.06</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1323</v>
+        <v>0.1929</v>
       </c>
       <c r="J179" t="n">
-        <v>3.969</v>
+        <v>5.787</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1323</v>
+        <v>0.1929</v>
       </c>
       <c r="J180" t="n">
-        <v>3.969</v>
+        <v>5.787</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.87</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5461</v>
+        <v>-0.4793</v>
       </c>
       <c r="J181" t="n">
-        <v>-16.383</v>
+        <v>-14.379</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.15</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4097</v>
+        <v>0.4109</v>
       </c>
       <c r="J182" t="n">
-        <v>10.2425</v>
+        <v>10.2725</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.91</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0776</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.94</v>
+        <v>-2.1875</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2462</v>
+        <v>-0.1984</v>
       </c>
       <c r="J184" t="n">
-        <v>-6.155</v>
+        <v>-4.96</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.6454</v>
+        <v>-0.4337</v>
       </c>
       <c r="J185" t="n">
-        <v>-16.135</v>
+        <v>-10.8425</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.29</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.9734</v>
+        <v>-0.6832</v>
       </c>
       <c r="J186" t="n">
-        <v>-24.335</v>
+        <v>-17.08</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.77</v>
       </c>
       <c r="I187" t="n">
-        <v>1.6695</v>
+        <v>1.1683</v>
       </c>
       <c r="J187" t="n">
-        <v>41.7375</v>
+        <v>29.2075</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.36</v>
       </c>
       <c r="I188" t="n">
-        <v>0.857</v>
+        <v>0.6665</v>
       </c>
       <c r="J188" t="n">
-        <v>21.425</v>
+        <v>16.6625</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.21</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4701</v>
+        <v>0.4677</v>
       </c>
       <c r="J189" t="n">
-        <v>11.7525</v>
+        <v>11.6925</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4454</v>
+        <v>0.4533</v>
       </c>
       <c r="J190" t="n">
-        <v>11.135</v>
+        <v>11.3325</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.08</v>
       </c>
       <c r="I191" t="n">
-        <v>0.13</v>
+        <v>0.2155</v>
       </c>
       <c r="J191" t="n">
-        <v>3.25</v>
+        <v>5.3875</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3603/event_3603_evp_summary.xlsx
+++ b/database/event/3603/event_3603_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.7355</v>
+        <v>8.382099999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7591</v>
+        <v>0.7284</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3056</v>
+        <v>3.1915</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7355</v>
+        <v>8.382099999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.7355</v>
+        <v>8.382099999999999</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2604</v>
+        <v>6.5889</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>6.2604</v>
+        <v>6.5889</v>
       </c>
       <c r="N2" t="n">
         <v>156</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.0923</v>
+        <v>7.8142</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7032</v>
+        <v>0.6791</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0153</v>
+        <v>2.933</v>
       </c>
       <c r="E3" t="n">
-        <v>8.0923</v>
+        <v>7.8142</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>8.0923</v>
+        <v>7.8142</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7994</v>
+        <v>6.1425</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>156</v>
       </c>
       <c r="M3" t="n">
-        <v>5.7994</v>
+        <v>6.1425</v>
       </c>
       <c r="N3" t="n">
         <v>156</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.8896</v>
+        <v>7.7415</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6856</v>
+        <v>0.6727</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9237</v>
+        <v>2.8999</v>
       </c>
       <c r="E4" t="n">
-        <v>7.8896</v>
+        <v>7.7415</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7.8896</v>
+        <v>7.7415</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>5.6542</v>
+        <v>6.0853</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>156</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6542</v>
+        <v>6.0853</v>
       </c>
       <c r="N4" t="n">
         <v>156</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7736</v>
+        <v>5.6359</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5017</v>
+        <v>0.4898</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9685</v>
+        <v>1.9414</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7736</v>
+        <v>5.6359</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5.7736</v>
+        <v>5.6359</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1377</v>
+        <v>4.4302</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>156</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1377</v>
+        <v>4.4302</v>
       </c>
       <c r="N5" t="n">
         <v>156</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9829</v>
+        <v>5.0282</v>
       </c>
       <c r="C6" t="n">
-        <v>0.433</v>
+        <v>0.437</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6115</v>
+        <v>1.6647</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9829</v>
+        <v>5.0282</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.9829</v>
+        <v>5.0282</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.571</v>
+        <v>3.9525</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>144</v>
       </c>
       <c r="M6" t="n">
-        <v>3.571</v>
+        <v>3.9525</v>
       </c>
       <c r="N6" t="n">
         <v>144</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6855</v>
+        <v>3.6775</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3203</v>
+        <v>0.3196</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0258</v>
+        <v>1.0499</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6855</v>
+        <v>3.6775</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6855</v>
+        <v>3.6775</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6412</v>
+        <v>2.8907</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>144</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6412</v>
+        <v>2.8907</v>
       </c>
       <c r="N7" t="n">
         <v>144</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5336</v>
+        <v>2.7397</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2202</v>
+        <v>0.2381</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5058</v>
+        <v>0.623</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5336</v>
+        <v>2.7397</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5336</v>
+        <v>2.7397</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8157</v>
+        <v>2.1536</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>156</v>
       </c>
       <c r="M8" t="n">
-        <v>1.8157</v>
+        <v>2.1536</v>
       </c>
       <c r="N8" t="n">
         <v>156</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.9257</v>
+        <v>2.0332</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1673</v>
+        <v>0.1767</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2313</v>
+        <v>0.3014</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9257</v>
+        <v>2.0332</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9257</v>
+        <v>2.0332</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3801</v>
+        <v>1.5982</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>128</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3801</v>
+        <v>1.5982</v>
       </c>
       <c r="N9" t="n">
         <v>128</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8914</v>
+        <v>1.9516</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1644</v>
+        <v>0.1696</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2159</v>
+        <v>0.2642</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8914</v>
+        <v>1.9516</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8914</v>
+        <v>1.9516</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3555</v>
+        <v>1.5341</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>144</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3555</v>
+        <v>1.5341</v>
       </c>
       <c r="N10" t="n">
         <v>144</v>
@@ -906,26 +906,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5921</v>
+        <v>1.689</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1384</v>
+        <v>0.1468</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.1447</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5921</v>
+        <v>1.689</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5921</v>
+        <v>1.689</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,44 +934,44 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.141</v>
+        <v>1.3277</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="M11" t="n">
-        <v>1.141</v>
+        <v>1.3277</v>
       </c>
       <c r="N11" t="n">
-        <v>77</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5218</v>
+        <v>1.6639</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1322</v>
+        <v>0.1446</v>
       </c>
       <c r="D12" t="n">
-        <v>0.049</v>
+        <v>0.1332</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5218</v>
+        <v>1.6639</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5218</v>
+        <v>1.6639</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,19 +980,19 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0906</v>
+        <v>1.3079</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="M12" t="n">
-        <v>1.0906</v>
+        <v>1.3079</v>
       </c>
       <c r="N12" t="n">
-        <v>233</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4816</v>
+        <v>1.5061</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1288</v>
+        <v>0.1309</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0309</v>
+        <v>0.0614</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4816</v>
+        <v>1.5061</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4816</v>
+        <v>1.5061</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0618</v>
+        <v>1.1839</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>233</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0618</v>
+        <v>1.1839</v>
       </c>
       <c r="N13" t="n">
         <v>233</v>
@@ -1044,26 +1044,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0966</v>
+        <v>1.1631</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0953</v>
+        <v>0.1011</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.143</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0966</v>
+        <v>1.1631</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0966</v>
+        <v>1.1631</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,44 +1072,44 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7859</v>
+        <v>0.9143</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>85</v>
+        <v>233</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7859</v>
+        <v>0.9143</v>
       </c>
       <c r="N14" t="n">
-        <v>85</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0677</v>
+        <v>1.0519</v>
       </c>
       <c r="C15" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0914</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.156</v>
+        <v>-0.1454</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0677</v>
+        <v>1.0519</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0677</v>
+        <v>1.0519</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7652</v>
+        <v>0.8269</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>233</v>
+        <v>85</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7652</v>
+        <v>0.8269</v>
       </c>
       <c r="N15" t="n">
-        <v>233</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>MINISE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9134</v>
+        <v>1.0304</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0794</v>
+        <v>0.0895</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2257</v>
+        <v>-0.1551</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9134</v>
+        <v>1.0304</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9134</v>
+        <v>1.0304</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6546</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6546</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>77</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MINISE</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8953</v>
+        <v>0.9843</v>
       </c>
       <c r="C17" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2338</v>
+        <v>-0.1761</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8953</v>
+        <v>0.9843</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8953</v>
+        <v>0.9843</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,19 +1210,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>233</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.821</v>
       </c>
       <c r="C18" t="n">
-        <v>0.067</v>
+        <v>0.0713</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2901</v>
+        <v>-0.2505</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.821</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.821</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5523</v>
+        <v>0.6454</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>77</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5523</v>
+        <v>0.6454</v>
       </c>
       <c r="N18" t="n">
         <v>77</v>
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.7382</v>
       </c>
       <c r="C19" t="n">
-        <v>0.065</v>
+        <v>0.0641</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3001</v>
+        <v>-0.2882</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.7382</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.7382</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5364</v>
+        <v>0.5803</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>77</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5364</v>
+        <v>0.5803</v>
       </c>
       <c r="N19" t="n">
         <v>77</v>
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5089</v>
+        <v>0.5179</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0442</v>
+        <v>0.045</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4083</v>
+        <v>-0.3884</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5089</v>
+        <v>0.5179</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5089</v>
+        <v>0.5179</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3647</v>
+        <v>0.4071</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>85</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3647</v>
+        <v>0.4071</v>
       </c>
       <c r="N20" t="n">
         <v>85</v>
@@ -1366,26 +1366,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>xeta</t>
+          <t>Subroza</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2577</v>
+        <v>0.4323</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0224</v>
+        <v>0.0376</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.4274</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2577</v>
+        <v>0.4323</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2577</v>
+        <v>0.4323</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,44 +1394,44 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1847</v>
+        <v>0.3398</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1847</v>
+        <v>0.3398</v>
       </c>
       <c r="N21" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Subroza</t>
+          <t>xeta</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.242</v>
+        <v>0.2745</v>
       </c>
       <c r="C22" t="n">
-        <v>0.021</v>
+        <v>0.0239</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5288</v>
+        <v>-0.4992</v>
       </c>
       <c r="E22" t="n">
-        <v>0.242</v>
+        <v>0.2745</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.242</v>
+        <v>0.2745</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,44 +1440,44 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1734</v>
+        <v>0.2158</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1734</v>
+        <v>0.2158</v>
       </c>
       <c r="N22" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>reatz</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0363</v>
+        <v>0.0849</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0032</v>
+        <v>0.0074</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6216</v>
+        <v>-0.5856</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0363</v>
+        <v>0.0849</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0363</v>
+        <v>0.0849</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,44 +1486,44 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.026</v>
+        <v>0.0667</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="M23" t="n">
-        <v>0.026</v>
+        <v>0.0667</v>
       </c>
       <c r="N23" t="n">
-        <v>77</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0022</v>
+        <v>0.081</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0002</v>
+        <v>0.007</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.637</v>
+        <v>-0.5873</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0022</v>
+        <v>0.081</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0022</v>
+        <v>0.081</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,19 +1532,19 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0016</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0016</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
@@ -1554,22 +1554,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0007</v>
+        <v>0.0321</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0001</v>
+        <v>0.0028</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6383</v>
+        <v>-0.6096</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0007</v>
+        <v>0.0321</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0007</v>
+        <v>0.0321</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0005</v>
+        <v>0.0252</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>128</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0005</v>
+        <v>0.0252</v>
       </c>
       <c r="N25" t="n">
         <v>128</v>
@@ -1596,26 +1596,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1058</v>
+        <v>-0.0262</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0092</v>
+        <v>-0.0023</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6858</v>
+        <v>-0.6361</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1058</v>
+        <v>-0.0262</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1058</v>
+        <v>-0.0262</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,19 +1624,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.0206</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.0206</v>
       </c>
       <c r="N26" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27">
@@ -1646,22 +1646,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1436</v>
+        <v>-0.1043</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0125</v>
+        <v>-0.0091</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7028</v>
+        <v>-0.6717</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1436</v>
+        <v>-0.1043</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1436</v>
+        <v>-0.1043</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.1029</v>
+        <v>-0.082</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>65</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1029</v>
+        <v>-0.082</v>
       </c>
       <c r="N27" t="n">
         <v>65</v>
@@ -1688,26 +1688,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>reatz</t>
+          <t>zeff</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1956</v>
+        <v>-0.2221</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.017</v>
+        <v>-0.0193</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1956</v>
+        <v>-0.2221</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.1956</v>
+        <v>-0.2221</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1402</v>
+        <v>-0.1746</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>233</v>
+        <v>128</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1402</v>
+        <v>-0.1746</v>
       </c>
       <c r="N28" t="n">
-        <v>233</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>zeff</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2605</v>
+        <v>-0.2231</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0226</v>
+        <v>-0.0194</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7556</v>
+        <v>-0.7258</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2605</v>
+        <v>-0.2231</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2605</v>
+        <v>-0.2231</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,19 +1762,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1867</v>
+        <v>-0.1754</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1867</v>
+        <v>-0.1754</v>
       </c>
       <c r="N29" t="n">
-        <v>128</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
@@ -1784,22 +1784,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2782</v>
+        <v>-0.3012</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0242</v>
+        <v>-0.0262</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7635999999999999</v>
+        <v>-0.7613</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2782</v>
+        <v>-0.3012</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2782</v>
+        <v>-0.3012</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.1994</v>
+        <v>-0.2368</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>85</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1994</v>
+        <v>-0.2368</v>
       </c>
       <c r="N30" t="n">
         <v>85</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4165</v>
+        <v>-0.3131</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0362</v>
+        <v>-0.0272</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.826</v>
+        <v>-0.7667</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4165</v>
+        <v>-0.3131</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.4165</v>
+        <v>-0.3131</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2985</v>
+        <v>-0.2461</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>65</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2985</v>
+        <v>-0.2461</v>
       </c>
       <c r="N31" t="n">
         <v>65</v>
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4563</v>
+        <v>-0.4403</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0397</v>
+        <v>-0.0383</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.844</v>
+        <v>-0.8246</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4563</v>
+        <v>-0.4403</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4563</v>
+        <v>-0.4403</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.327</v>
+        <v>-0.3461</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>65</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.327</v>
+        <v>-0.3461</v>
       </c>
       <c r="N32" t="n">
         <v>65</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5329</v>
+        <v>-0.509</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0463</v>
+        <v>-0.0442</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8786</v>
+        <v>-0.8559</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5329</v>
+        <v>-0.509</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.5329</v>
+        <v>-0.509</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.3819</v>
+        <v>-0.4001</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>65</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3819</v>
+        <v>-0.4001</v>
       </c>
       <c r="N33" t="n">
         <v>65</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0896</v>
+        <v>-1.0512</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.1299</v>
+        <v>-1.1027</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0896</v>
+        <v>-1.0512</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.0896</v>
+        <v>-1.0512</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7809</v>
+        <v>-0.8263</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>36</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7809</v>
+        <v>-0.8263</v>
       </c>
       <c r="N34" t="n">
         <v>36</v>
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1556</v>
+        <v>-1.0654</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1004</v>
+        <v>-0.0926</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1597</v>
+        <v>-1.1092</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1556</v>
+        <v>-1.0654</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.1556</v>
+        <v>-1.0654</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8282</v>
+        <v>-0.8375</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>85</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8282</v>
+        <v>-0.8375</v>
       </c>
       <c r="N35" t="n">
         <v>85</v>
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1674</v>
+        <v>-1.1159</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1014</v>
+        <v>-0.097</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.165</v>
+        <v>-1.1322</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1674</v>
+        <v>-1.1159</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.1674</v>
+        <v>-1.1159</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8366</v>
+        <v>-0.8772</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>36</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8366</v>
+        <v>-0.8772</v>
       </c>
       <c r="N36" t="n">
         <v>36</v>
@@ -2106,22 +2106,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2968</v>
+        <v>-1.2317</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1127</v>
+        <v>-0.107</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2235</v>
+        <v>-1.1849</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2968</v>
+        <v>-1.2317</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.2968</v>
+        <v>-1.2317</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9294</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>85</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9294</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>85</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3954</v>
+        <v>-1.2722</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1213</v>
+        <v>-0.1106</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.268</v>
+        <v>-1.2033</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3954</v>
+        <v>-1.2722</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.3954</v>
+        <v>-1.2722</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3954</v>
+        <v>-1.2722</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1213</v>
+        <v>-0.1106</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.268</v>
+        <v>-1.2033</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3954</v>
+        <v>-1.2722</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.3954</v>
+        <v>-1.2722</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4526</v>
+        <v>-1.3195</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1262</v>
+        <v>-0.1147</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2938</v>
+        <v>-1.2249</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4526</v>
+        <v>-1.3195</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.4526</v>
+        <v>-1.3195</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.041</v>
+        <v>-1.0372</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>128</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.041</v>
+        <v>-1.0372</v>
       </c>
       <c r="N40" t="n">
         <v>128</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6982</v>
+        <v>-1.4947</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1476</v>
+        <v>-0.1299</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4047</v>
+        <v>-1.3046</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6982</v>
+        <v>-1.4947</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.6982</v>
+        <v>-1.4947</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.217</v>
+        <v>-1.1749</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>144</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.217</v>
+        <v>-1.1749</v>
       </c>
       <c r="N41" t="n">
         <v>144</v>
@@ -2429,10 +2429,10 @@
         <v>0.7</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2776</v>
+        <v>-0.3022</v>
       </c>
       <c r="J2" t="n">
-        <v>-6.1072</v>
+        <v>-6.6484</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2878</v>
+        <v>-0.312</v>
       </c>
       <c r="J3" t="n">
-        <v>-6.3316</v>
+        <v>-6.864</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.63</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3464</v>
+        <v>-0.3678</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.6208</v>
+        <v>-8.0916</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4085</v>
+        <v>-0.4271</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.987</v>
+        <v>-9.3962</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.4</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5592</v>
+        <v>-0.5677</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.3024</v>
+        <v>-12.4894</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.65</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2682</v>
+        <v>1.3378</v>
       </c>
       <c r="J7" t="n">
-        <v>27.9004</v>
+        <v>29.4316</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.62</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2335</v>
+        <v>1.2875</v>
       </c>
       <c r="J8" t="n">
-        <v>27.137</v>
+        <v>28.325</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2103</v>
+        <v>1.2538</v>
       </c>
       <c r="J9" t="n">
-        <v>26.6266</v>
+        <v>27.5836</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.49</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0829</v>
+        <v>1.0672</v>
       </c>
       <c r="J10" t="n">
-        <v>23.8238</v>
+        <v>23.4784</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2652</v>
+        <v>0.2905</v>
       </c>
       <c r="J11" t="n">
-        <v>5.8344</v>
+        <v>6.391</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.34</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6745</v>
+        <v>0.6513</v>
       </c>
       <c r="J12" t="n">
-        <v>20.235</v>
+        <v>19.539</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3557</v>
+        <v>0.358</v>
       </c>
       <c r="J13" t="n">
-        <v>10.671</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0626</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>1.878</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1376</v>
+        <v>-0.1495</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.128</v>
+        <v>-4.485</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.73</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.311</v>
+        <v>-0.3225</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.33</v>
+        <v>-9.675000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.19</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5689</v>
+        <v>0.546</v>
       </c>
       <c r="J17" t="n">
-        <v>17.067</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.19</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5689</v>
+        <v>0.546</v>
       </c>
       <c r="J18" t="n">
-        <v>17.067</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.17</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5174</v>
+        <v>0.4998</v>
       </c>
       <c r="J19" t="n">
-        <v>15.522</v>
+        <v>14.994</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.05</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1839</v>
+        <v>0.1912</v>
       </c>
       <c r="J20" t="n">
-        <v>5.517</v>
+        <v>5.736</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.73</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8181</v>
+        <v>-0.7575</v>
       </c>
       <c r="J21" t="n">
-        <v>-24.543</v>
+        <v>-22.725</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.77</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1752</v>
+        <v>-0.2088</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.9784</v>
+        <v>-3.5496</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.74</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2098</v>
+        <v>-0.2417</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.5666</v>
+        <v>-4.1089</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.67</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2869</v>
+        <v>-0.3147</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.8773</v>
+        <v>-5.3499</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.25</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6937</v>
+        <v>-0.6922</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.7929</v>
+        <v>-11.7674</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.21</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7338</v>
+        <v>-0.7285</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.4746</v>
+        <v>-12.3845</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>2.63</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J27" t="n">
-        <v>31.7577</v>
+        <v>31.3701</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.68</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2844</v>
+        <v>1.3663</v>
       </c>
       <c r="J28" t="n">
-        <v>21.8348</v>
+        <v>23.2271</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.49</v>
       </c>
       <c r="I29" t="n">
-        <v>1.0681</v>
+        <v>1.0499</v>
       </c>
       <c r="J29" t="n">
-        <v>18.1577</v>
+        <v>17.8483</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.31</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7294</v>
+        <v>0.713</v>
       </c>
       <c r="J30" t="n">
-        <v>12.3998</v>
+        <v>12.121</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.16</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3689</v>
+        <v>0.3914</v>
       </c>
       <c r="J31" t="n">
-        <v>6.2713</v>
+        <v>6.6538</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.05</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1884</v>
+        <v>0.1836</v>
       </c>
       <c r="J32" t="n">
-        <v>4.71</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0804</v>
+        <v>0.0742</v>
       </c>
       <c r="J33" t="n">
-        <v>2.01</v>
+        <v>1.855</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.85</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1708</v>
+        <v>-0.1883</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.27</v>
+        <v>-4.7075</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.74</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2778</v>
+        <v>-0.2947</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.945</v>
+        <v>-7.3675</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.55</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4566</v>
+        <v>-0.4663</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.415</v>
+        <v>-11.6575</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6781</v>
+        <v>0.7532</v>
       </c>
       <c r="J37" t="n">
-        <v>16.9525</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.35</v>
       </c>
       <c r="I38" t="n">
-        <v>0.665</v>
+        <v>0.7388</v>
       </c>
       <c r="J38" t="n">
-        <v>16.625</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.29</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5854</v>
+        <v>0.6511</v>
       </c>
       <c r="J39" t="n">
-        <v>14.635</v>
+        <v>16.2775</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.22</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4916</v>
+        <v>0.546</v>
       </c>
       <c r="J40" t="n">
-        <v>12.29</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.98</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1546</v>
+        <v>-0.1418</v>
       </c>
       <c r="J41" t="n">
-        <v>-3.865</v>
+        <v>-3.545</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.26</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4803</v>
+        <v>0.528</v>
       </c>
       <c r="J42" t="n">
-        <v>12.4878</v>
+        <v>13.728</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.09</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2509</v>
+        <v>0.251</v>
       </c>
       <c r="J43" t="n">
-        <v>6.5234</v>
+        <v>6.526</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.92</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1038</v>
+        <v>-0.1176</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.6988</v>
+        <v>-3.0576</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.87</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1571</v>
+        <v>-0.1727</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.0846</v>
+        <v>-4.4902</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.43</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5737</v>
+        <v>-0.5753</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.9162</v>
+        <v>-14.9578</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.46</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8131</v>
+        <v>0.8988</v>
       </c>
       <c r="J47" t="n">
-        <v>21.1406</v>
+        <v>23.3688</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6561</v>
+        <v>0.7281</v>
       </c>
       <c r="J48" t="n">
-        <v>17.0586</v>
+        <v>18.9306</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.27</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5619</v>
+        <v>0.6241</v>
       </c>
       <c r="J49" t="n">
-        <v>14.6094</v>
+        <v>16.2266</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.02</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0439</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>1.1414</v>
+        <v>1.6952</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.98</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1482</v>
+        <v>-0.1373</v>
       </c>
       <c r="J51" t="n">
-        <v>-3.8532</v>
+        <v>-3.5698</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8537</v>
+        <v>0.9396</v>
       </c>
       <c r="J52" t="n">
-        <v>25.611</v>
+        <v>28.188</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5433</v>
+        <v>0.6012</v>
       </c>
       <c r="J53" t="n">
-        <v>16.299</v>
+        <v>18.036</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.24</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5292</v>
+        <v>0.5855</v>
       </c>
       <c r="J54" t="n">
-        <v>15.876</v>
+        <v>17.565</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.12</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3539</v>
+        <v>0.368</v>
       </c>
       <c r="J55" t="n">
-        <v>10.617</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.9625</v>
+        <v>-0.8797</v>
       </c>
       <c r="J56" t="n">
-        <v>-28.875</v>
+        <v>-26.391</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.31</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5084</v>
+        <v>0.5652</v>
       </c>
       <c r="J57" t="n">
-        <v>15.252</v>
+        <v>16.956</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4149</v>
+        <v>0.4573</v>
       </c>
       <c r="J58" t="n">
-        <v>12.447</v>
+        <v>13.719</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.02</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0644</v>
+        <v>0.0722</v>
       </c>
       <c r="J59" t="n">
-        <v>1.932</v>
+        <v>2.166</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2404</v>
+        <v>-0.2535</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.212</v>
+        <v>-7.605</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3281</v>
+        <v>-0.3395</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.843</v>
+        <v>-10.185</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.13</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2994</v>
+        <v>0.2915</v>
       </c>
       <c r="J62" t="n">
-        <v>7.485</v>
+        <v>7.2875</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.75</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2619</v>
+        <v>-0.2804</v>
       </c>
       <c r="J63" t="n">
-        <v>-6.5475</v>
+        <v>-7.01</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.73</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2809</v>
+        <v>-0.299</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.0225</v>
+        <v>-7.475</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.68</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3283</v>
+        <v>-0.345</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.2075</v>
+        <v>-8.625</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.67</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3378</v>
+        <v>-0.3541</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.445</v>
+        <v>-8.852499999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6009</v>
+        <v>0.6905</v>
       </c>
       <c r="J67" t="n">
-        <v>15.0225</v>
+        <v>17.2625</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.56</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5331</v>
+        <v>0.6118</v>
       </c>
       <c r="J68" t="n">
-        <v>13.3275</v>
+        <v>15.295</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.27</v>
       </c>
       <c r="I69" t="n">
-        <v>0.347</v>
+        <v>0.3741</v>
       </c>
       <c r="J69" t="n">
-        <v>8.675000000000001</v>
+        <v>9.352499999999999</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0264</v>
+        <v>-0.0204</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.66</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.91</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1516</v>
+        <v>-0.1577</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.79</v>
+        <v>-3.9425</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.52</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9033</v>
+        <v>0.9932</v>
       </c>
       <c r="J72" t="n">
-        <v>21.6792</v>
+        <v>23.8368</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7597</v>
+        <v>0.8387</v>
       </c>
       <c r="J73" t="n">
-        <v>18.2328</v>
+        <v>20.1288</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.13</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3686</v>
+        <v>0.3912</v>
       </c>
       <c r="J74" t="n">
-        <v>8.846399999999999</v>
+        <v>9.3888</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.88</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4509</v>
+        <v>-0.4256</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.8216</v>
+        <v>-10.2144</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.87</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4788</v>
+        <v>-0.451</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.4912</v>
+        <v>-10.824</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4214</v>
+        <v>0.4662</v>
       </c>
       <c r="J77" t="n">
-        <v>10.1136</v>
+        <v>11.1888</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3572</v>
+        <v>0.3748</v>
       </c>
       <c r="J78" t="n">
-        <v>8.572800000000001</v>
+        <v>8.995200000000001</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.01</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0337</v>
+        <v>0.0405</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8088</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1491</v>
+        <v>-0.1612</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.5784</v>
+        <v>-3.8688</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1707</v>
+        <v>-0.1832</v>
       </c>
       <c r="J81" t="n">
-        <v>-4.0968</v>
+        <v>-4.3968</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.96</v>
       </c>
       <c r="I82" t="n">
-        <v>1.344</v>
+        <v>1.4737</v>
       </c>
       <c r="J82" t="n">
-        <v>25.536</v>
+        <v>28.0003</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.88</v>
       </c>
       <c r="I83" t="n">
-        <v>1.2547</v>
+        <v>1.3799</v>
       </c>
       <c r="J83" t="n">
-        <v>23.8393</v>
+        <v>26.2181</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.75</v>
       </c>
       <c r="I84" t="n">
-        <v>1.1077</v>
+        <v>1.2246</v>
       </c>
       <c r="J84" t="n">
-        <v>21.0463</v>
+        <v>23.2674</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1157</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J85" t="n">
-        <v>-2.1983</v>
+        <v>-1.5333</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.93</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3793</v>
+        <v>-0.3432</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.2067</v>
+        <v>-6.5208</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.96</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0716</v>
+        <v>0.0132</v>
       </c>
       <c r="J87" t="n">
-        <v>1.3604</v>
+        <v>0.2508</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.58</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.3891</v>
+        <v>-0.409</v>
       </c>
       <c r="J88" t="n">
-        <v>-7.3929</v>
+        <v>-7.771</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.54</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.425</v>
+        <v>-0.443</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.074999999999999</v>
+        <v>-8.417</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.47</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4905</v>
+        <v>-0.5043</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.3195</v>
+        <v>-9.5817</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.38</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5766</v>
+        <v>-0.5839</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.9554</v>
+        <v>-11.0941</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>2.12</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4823</v>
+        <v>1.624</v>
       </c>
       <c r="J92" t="n">
-        <v>25.1991</v>
+        <v>27.608</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.88</v>
       </c>
       <c r="I93" t="n">
-        <v>1.2254</v>
+        <v>1.3542</v>
       </c>
       <c r="J93" t="n">
-        <v>20.8318</v>
+        <v>23.0214</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.57</v>
       </c>
       <c r="I94" t="n">
-        <v>0.8857</v>
+        <v>0.9902</v>
       </c>
       <c r="J94" t="n">
-        <v>15.0569</v>
+        <v>16.8334</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.5</v>
       </c>
       <c r="I95" t="n">
-        <v>0.8032</v>
+        <v>0.9008</v>
       </c>
       <c r="J95" t="n">
-        <v>13.6544</v>
+        <v>15.3136</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.36</v>
       </c>
       <c r="I96" t="n">
-        <v>0.6291</v>
+        <v>0.7108</v>
       </c>
       <c r="J96" t="n">
-        <v>10.6947</v>
+        <v>12.0836</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>0.76</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.1474</v>
+        <v>-0.1886</v>
       </c>
       <c r="J97" t="n">
-        <v>-2.5058</v>
+        <v>-3.2062</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.58</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.3559</v>
+        <v>-0.3833</v>
       </c>
       <c r="J98" t="n">
-        <v>-6.0503</v>
+        <v>-6.5161</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.49</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4475</v>
+        <v>-0.4682</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.6075</v>
+        <v>-7.9594</v>
       </c>
     </row>
     <row r="100">
@@ -6389,10 +6389,10 @@
         <v>0.23</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7019</v>
+        <v>-0.7009</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.9323</v>
+        <v>-11.9153</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4852</v>
+        <v>0.5416</v>
       </c>
       <c r="J102" t="n">
-        <v>14.0708</v>
+        <v>15.7064</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.23</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4142</v>
+        <v>0.4593</v>
       </c>
       <c r="J103" t="n">
-        <v>12.0118</v>
+        <v>13.3197</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0264</v>
+        <v>0.0353</v>
       </c>
       <c r="J104" t="n">
-        <v>0.7655999999999999</v>
+        <v>1.0237</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0277</v>
+        <v>-0.0307</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.8033</v>
+        <v>-0.8903</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.86</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1862</v>
+        <v>-0.1977</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.3998</v>
+        <v>-5.7333</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.2</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4937</v>
+        <v>0.5403</v>
       </c>
       <c r="J107" t="n">
-        <v>14.3173</v>
+        <v>15.6687</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.17</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4478</v>
+        <v>0.4888</v>
       </c>
       <c r="J108" t="n">
-        <v>12.9862</v>
+        <v>14.1752</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.05</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1881</v>
+        <v>0.1941</v>
       </c>
       <c r="J109" t="n">
-        <v>5.4549</v>
+        <v>5.6289</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0871</v>
+        <v>0.0951</v>
       </c>
       <c r="J110" t="n">
-        <v>2.5259</v>
+        <v>2.7579</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.75</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7603</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-22.0487</v>
+        <v>-20.5378</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.88</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6994</v>
+        <v>0.8087</v>
       </c>
       <c r="J112" t="n">
-        <v>14.6874</v>
+        <v>16.9827</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.84</v>
       </c>
       <c r="I113" t="n">
-        <v>0.6768</v>
+        <v>0.7827</v>
       </c>
       <c r="J113" t="n">
-        <v>14.2128</v>
+        <v>16.4367</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.52</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4922</v>
+        <v>0.5675</v>
       </c>
       <c r="J114" t="n">
-        <v>10.3362</v>
+        <v>11.9175</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.28</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3403</v>
+        <v>0.3691</v>
       </c>
       <c r="J115" t="n">
-        <v>7.1463</v>
+        <v>7.7511</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.99</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0654</v>
+        <v>-0.0602</v>
       </c>
       <c r="J116" t="n">
-        <v>-1.3734</v>
+        <v>-1.2642</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>0.413</v>
+        <v>0.4347</v>
       </c>
       <c r="J117" t="n">
-        <v>8.673</v>
+        <v>9.1287</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.78</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2141</v>
+        <v>-0.2375</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.4961</v>
+        <v>-4.9875</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.58</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4028</v>
+        <v>-0.4196</v>
       </c>
       <c r="J119" t="n">
-        <v>-8.4588</v>
+        <v>-8.8116</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.42</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.5601</v>
       </c>
       <c r="J120" t="n">
-        <v>-11.6109</v>
+        <v>-11.7621</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.38</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5905</v>
+        <v>-0.5949</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.4005</v>
+        <v>-12.4929</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.44</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6504</v>
+        <v>0.7229</v>
       </c>
       <c r="J122" t="n">
-        <v>17.5608</v>
+        <v>19.5183</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.06</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1697</v>
+        <v>0.1759</v>
       </c>
       <c r="J123" t="n">
-        <v>4.5819</v>
+        <v>4.7493</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.91</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1194</v>
+        <v>-0.1326</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.2238</v>
+        <v>-3.5802</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.71</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3228</v>
+        <v>-0.3354</v>
       </c>
       <c r="J125" t="n">
-        <v>-8.7156</v>
+        <v>-9.0558</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.71</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3228</v>
+        <v>-0.3354</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.7156</v>
+        <v>-9.0558</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.65</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0587</v>
+        <v>1.1601</v>
       </c>
       <c r="J127" t="n">
-        <v>28.5849</v>
+        <v>31.3227</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.17</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4253</v>
+        <v>0.4694</v>
       </c>
       <c r="J128" t="n">
-        <v>11.4831</v>
+        <v>12.6738</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.08</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2463</v>
+        <v>0.2577</v>
       </c>
       <c r="J129" t="n">
-        <v>6.6501</v>
+        <v>6.9579</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.04</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1207</v>
+        <v>0.1388</v>
       </c>
       <c r="J130" t="n">
-        <v>3.2589</v>
+        <v>3.7476</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.03</v>
       </c>
       <c r="I131" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1052</v>
       </c>
       <c r="J131" t="n">
-        <v>2.322</v>
+        <v>2.8404</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.92</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0877</v>
+        <v>-0.1052</v>
       </c>
       <c r="J132" t="n">
-        <v>-2.1048</v>
+        <v>-2.5248</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.9</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1112</v>
+        <v>-0.1293</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.6688</v>
+        <v>-3.1032</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2062</v>
+        <v>-0.2249</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.9488</v>
+        <v>-5.3976</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.7</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3105</v>
+        <v>-0.3276</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.452</v>
+        <v>-7.8624</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.67</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.339</v>
+        <v>-0.355</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.135999999999999</v>
+        <v>-8.52</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.95</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3782</v>
+        <v>1.5022</v>
       </c>
       <c r="J137" t="n">
-        <v>33.0768</v>
+        <v>36.0528</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.94</v>
       </c>
       <c r="I138" t="n">
-        <v>1.3666</v>
+        <v>1.4902</v>
       </c>
       <c r="J138" t="n">
-        <v>32.7984</v>
+        <v>35.7648</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2731</v>
+        <v>0.2898</v>
       </c>
       <c r="J139" t="n">
-        <v>6.5544</v>
+        <v>6.9552</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5718</v>
+        <v>-0.5274</v>
       </c>
       <c r="J140" t="n">
-        <v>-13.7232</v>
+        <v>-12.6576</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.6676</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.4792</v>
+        <v>-16.0224</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.47</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4796</v>
+        <v>0.5483</v>
       </c>
       <c r="J142" t="n">
-        <v>11.0308</v>
+        <v>12.6109</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.4</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4344</v>
+        <v>0.495</v>
       </c>
       <c r="J143" t="n">
-        <v>9.991199999999999</v>
+        <v>11.385</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.15</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2141</v>
+        <v>0.2336</v>
       </c>
       <c r="J144" t="n">
-        <v>4.9243</v>
+        <v>5.3728</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.14</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2009</v>
+        <v>0.2205</v>
       </c>
       <c r="J145" t="n">
-        <v>4.6207</v>
+        <v>5.0715</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>0.146</v>
+        <v>0.1655</v>
       </c>
       <c r="J146" t="n">
-        <v>3.358</v>
+        <v>3.8065</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.92</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.1095</v>
       </c>
       <c r="J147" t="n">
-        <v>-2.1436</v>
+        <v>-2.5185</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.92</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.1095</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.1436</v>
+        <v>-2.5185</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.91</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1049</v>
+        <v>-0.1215</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.4127</v>
+        <v>-2.7945</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.78</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2378</v>
+        <v>-0.2557</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.4694</v>
+        <v>-5.8811</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.62</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3903</v>
+        <v>-0.4034</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.976900000000001</v>
+        <v>-9.2782</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.92</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0567</v>
+        <v>-0.0809</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.0206</v>
+        <v>-1.4562</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.77</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2268</v>
+        <v>-0.2494</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.0824</v>
+        <v>-4.4892</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.74</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.257</v>
+        <v>-0.2787</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.626</v>
+        <v>-5.0166</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.67</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3217</v>
+        <v>-0.3417</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.7906</v>
+        <v>-6.1506</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.3</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6669</v>
+        <v>-0.6651</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.0042</v>
+        <v>-11.9718</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.71</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0735</v>
+        <v>1.186</v>
       </c>
       <c r="J157" t="n">
-        <v>19.323</v>
+        <v>21.348</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.66</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0152</v>
+        <v>1.1239</v>
       </c>
       <c r="J158" t="n">
-        <v>18.2736</v>
+        <v>20.2302</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.39</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6944</v>
+        <v>0.7763</v>
       </c>
       <c r="J159" t="n">
-        <v>12.4992</v>
+        <v>13.9734</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.35</v>
       </c>
       <c r="I160" t="n">
-        <v>0.6438</v>
+        <v>0.7207</v>
       </c>
       <c r="J160" t="n">
-        <v>11.5884</v>
+        <v>12.9726</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.07</v>
       </c>
       <c r="I161" t="n">
-        <v>0.161</v>
+        <v>0.191</v>
       </c>
       <c r="J161" t="n">
-        <v>2.898</v>
+        <v>3.438</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.37</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4421</v>
+        <v>0.4978</v>
       </c>
       <c r="J162" t="n">
-        <v>13.263</v>
+        <v>14.934</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.16</v>
       </c>
       <c r="I163" t="n">
-        <v>0.254</v>
+        <v>0.2666</v>
       </c>
       <c r="J163" t="n">
-        <v>7.62</v>
+        <v>7.998</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.98</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0383</v>
+        <v>-0.0445</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.149</v>
+        <v>-1.335</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.89</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1482</v>
+        <v>-0.1605</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.446</v>
+        <v>-4.815</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.73</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3105</v>
+        <v>-0.3221</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.315</v>
+        <v>-9.663</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.63</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6479</v>
+        <v>0.7287</v>
       </c>
       <c r="J167" t="n">
-        <v>19.437</v>
+        <v>21.861</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.18</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2954</v>
+        <v>0.3039</v>
       </c>
       <c r="J168" t="n">
-        <v>8.862</v>
+        <v>9.117000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.16</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2673</v>
+        <v>0.2768</v>
       </c>
       <c r="J169" t="n">
-        <v>8.019</v>
+        <v>8.304</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3233</v>
+        <v>-0.334</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.699</v>
+        <v>-10.02</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.59</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4438</v>
+        <v>-0.4503</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.314</v>
+        <v>-13.509</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.04</v>
       </c>
       <c r="I172" t="n">
-        <v>0.121</v>
+        <v>0.1282</v>
       </c>
       <c r="J172" t="n">
-        <v>3.63</v>
+        <v>3.846</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.04</v>
       </c>
       <c r="I173" t="n">
-        <v>0.121</v>
+        <v>0.1282</v>
       </c>
       <c r="J173" t="n">
-        <v>3.63</v>
+        <v>3.846</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0032</v>
+        <v>0.0022</v>
       </c>
       <c r="J174" t="n">
-        <v>0.096</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0736</v>
+        <v>-0.0843</v>
       </c>
       <c r="J175" t="n">
-        <v>-2.208</v>
+        <v>-2.529</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.85</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1852</v>
+        <v>-0.1993</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.556</v>
+        <v>-5.979</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.45</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8119</v>
+        <v>0.8952</v>
       </c>
       <c r="J177" t="n">
-        <v>24.357</v>
+        <v>26.856</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.38</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.795</v>
       </c>
       <c r="J178" t="n">
-        <v>21.579</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.06</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1929</v>
+        <v>0.2058</v>
       </c>
       <c r="J179" t="n">
-        <v>5.787</v>
+        <v>6.174</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1929</v>
+        <v>0.2058</v>
       </c>
       <c r="J180" t="n">
-        <v>5.787</v>
+        <v>6.174</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.87</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4793</v>
+        <v>-0.4513</v>
       </c>
       <c r="J181" t="n">
-        <v>-14.379</v>
+        <v>-13.539</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.15</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4109</v>
+        <v>0.4321</v>
       </c>
       <c r="J182" t="n">
-        <v>10.2725</v>
+        <v>10.8025</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.91</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.108</v>
       </c>
       <c r="J183" t="n">
-        <v>-2.1875</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1984</v>
+        <v>-0.2189</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.96</v>
+        <v>-5.4725</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4337</v>
+        <v>-0.4468</v>
       </c>
       <c r="J185" t="n">
-        <v>-10.8425</v>
+        <v>-11.17</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.29</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6832</v>
+        <v>-0.6792</v>
       </c>
       <c r="J186" t="n">
-        <v>-17.08</v>
+        <v>-16.98</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.77</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1683</v>
+        <v>1.282</v>
       </c>
       <c r="J187" t="n">
-        <v>29.2075</v>
+        <v>32.05</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.36</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6665</v>
+        <v>0.7432</v>
       </c>
       <c r="J188" t="n">
-        <v>16.6625</v>
+        <v>18.58</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.21</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4677</v>
+        <v>0.5216</v>
       </c>
       <c r="J189" t="n">
-        <v>11.6925</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4533</v>
+        <v>0.5054</v>
       </c>
       <c r="J190" t="n">
-        <v>11.3325</v>
+        <v>12.635</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.08</v>
       </c>
       <c r="I191" t="n">
-        <v>0.2155</v>
+        <v>0.2363</v>
       </c>
       <c r="J191" t="n">
-        <v>5.3875</v>
+        <v>5.9075</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3603/event_3603_evp_summary.xlsx
+++ b/database/event/3603/event_3603_evp_summary.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.382099999999999</v>
+        <v>8.305</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7284</v>
+        <v>0.7217</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1915</v>
+        <v>3.1775</v>
       </c>
       <c r="E2" t="n">
-        <v>8.382099999999999</v>
+        <v>8.305</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>8.382099999999999</v>
+        <v>8.305</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -520,7 +520,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>6.5889</v>
+        <v>6.5661</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>6.5889</v>
+        <v>6.5661</v>
       </c>
       <c r="N2" t="n">
         <v>156</v>
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.8142</v>
+        <v>7.9528</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6791</v>
+        <v>0.6911</v>
       </c>
       <c r="D3" t="n">
-        <v>2.933</v>
+        <v>3.0171</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8142</v>
+        <v>7.9528</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8142</v>
+        <v>7.9528</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6.1425</v>
+        <v>6.2876</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>156</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1425</v>
+        <v>6.2876</v>
       </c>
       <c r="N3" t="n">
         <v>156</v>
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.7415</v>
+        <v>7.6414</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6727</v>
+        <v>0.664</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8999</v>
+        <v>2.8752</v>
       </c>
       <c r="E4" t="n">
-        <v>7.7415</v>
+        <v>7.6414</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7.7415</v>
+        <v>7.6414</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6.0853</v>
+        <v>6.0414</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>156</v>
       </c>
       <c r="M4" t="n">
-        <v>6.0853</v>
+        <v>6.0414</v>
       </c>
       <c r="N4" t="n">
         <v>156</v>
@@ -634,22 +634,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6359</v>
+        <v>5.5284</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4898</v>
+        <v>0.4804</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9414</v>
+        <v>1.9127</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6359</v>
+        <v>5.5284</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6359</v>
+        <v>5.5284</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4302</v>
+        <v>4.3709</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>156</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4302</v>
+        <v>4.3709</v>
       </c>
       <c r="N5" t="n">
         <v>156</v>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.0282</v>
+        <v>4.8533</v>
       </c>
       <c r="C6" t="n">
-        <v>0.437</v>
+        <v>0.4218</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6647</v>
+        <v>1.6051</v>
       </c>
       <c r="E6" t="n">
-        <v>5.0282</v>
+        <v>4.8533</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>5.0282</v>
+        <v>4.8533</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9525</v>
+        <v>3.8371</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>144</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9525</v>
+        <v>3.8371</v>
       </c>
       <c r="N6" t="n">
         <v>144</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6775</v>
+        <v>3.6097</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3196</v>
+        <v>0.3137</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0499</v>
+        <v>1.0386</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6775</v>
+        <v>3.6097</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6775</v>
+        <v>3.6097</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8907</v>
+        <v>2.8539</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>144</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8907</v>
+        <v>2.8539</v>
       </c>
       <c r="N7" t="n">
         <v>144</v>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7397</v>
+        <v>2.8981</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2381</v>
+        <v>0.2518</v>
       </c>
       <c r="D8" t="n">
-        <v>0.623</v>
+        <v>0.7144</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7397</v>
+        <v>2.8981</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7397</v>
+        <v>2.8981</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1536</v>
+        <v>2.2913</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>156</v>
       </c>
       <c r="M8" t="n">
-        <v>2.1536</v>
+        <v>2.2913</v>
       </c>
       <c r="N8" t="n">
         <v>156</v>
@@ -818,22 +818,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.0332</v>
+        <v>2.0155</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1767</v>
+        <v>0.1751</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3014</v>
+        <v>0.3124</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0332</v>
+        <v>2.0155</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0332</v>
+        <v>2.0155</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5982</v>
+        <v>1.5935</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>128</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5982</v>
+        <v>1.5935</v>
       </c>
       <c r="N9" t="n">
         <v>128</v>
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9516</v>
+        <v>1.9013</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1696</v>
+        <v>0.1652</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2642</v>
+        <v>0.2603</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9516</v>
+        <v>1.9013</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9516</v>
+        <v>1.9013</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5341</v>
+        <v>1.5032</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>144</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5341</v>
+        <v>1.5032</v>
       </c>
       <c r="N10" t="n">
         <v>144</v>
@@ -910,22 +910,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.689</v>
+        <v>1.6205</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1468</v>
+        <v>0.1408</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1447</v>
+        <v>0.1324</v>
       </c>
       <c r="E11" t="n">
-        <v>1.689</v>
+        <v>1.6205</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.689</v>
+        <v>1.6205</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3277</v>
+        <v>1.2812</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>233</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3277</v>
+        <v>1.2812</v>
       </c>
       <c r="N11" t="n">
         <v>233</v>
@@ -956,22 +956,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6639</v>
+        <v>1.5655</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1446</v>
+        <v>0.136</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1332</v>
+        <v>0.1074</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6639</v>
+        <v>1.5655</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6639</v>
+        <v>1.5655</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3079</v>
+        <v>1.2377</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>77</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3079</v>
+        <v>1.2377</v>
       </c>
       <c r="N12" t="n">
         <v>77</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5061</v>
+        <v>1.4659</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1309</v>
+        <v>0.1274</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0614</v>
+        <v>0.062</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5061</v>
+        <v>1.4659</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5061</v>
+        <v>1.4659</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1839</v>
+        <v>1.159</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>233</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1839</v>
+        <v>1.159</v>
       </c>
       <c r="N13" t="n">
         <v>233</v>
@@ -1044,26 +1044,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>MINISE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1631</v>
+        <v>1.1575</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1011</v>
+        <v>0.1006</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0785</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1631</v>
+        <v>1.1575</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1631</v>
+        <v>1.1575</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9143</v>
+        <v>0.9151</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>233</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9143</v>
+        <v>0.9151</v>
       </c>
       <c r="N14" t="n">
         <v>233</v>
@@ -1090,26 +1090,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0519</v>
+        <v>1.0501</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0914</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1454</v>
+        <v>-0.1274</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0519</v>
+        <v>1.0501</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0519</v>
+        <v>1.0501</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1118,44 +1118,44 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8269</v>
+        <v>0.8302</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>85</v>
+        <v>233</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8269</v>
+        <v>0.8302</v>
       </c>
       <c r="N15" t="n">
-        <v>85</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MINISE</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0304</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0895</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1551</v>
+        <v>-0.1881</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0304</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0304</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,44 +1164,44 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7249</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7249</v>
       </c>
       <c r="N16" t="n">
-        <v>233</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9843</v>
+        <v>0.8843</v>
       </c>
       <c r="C17" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1761</v>
+        <v>-0.2029</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9843</v>
+        <v>0.8843</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9843</v>
+        <v>0.8843</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1210,19 +1210,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
@@ -1232,22 +1232,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.821</v>
+        <v>0.7792</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0713</v>
+        <v>0.0677</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2505</v>
+        <v>-0.2508</v>
       </c>
       <c r="E18" t="n">
-        <v>0.821</v>
+        <v>0.7792</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.821</v>
+        <v>0.7792</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6454</v>
+        <v>0.616</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>77</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6454</v>
+        <v>0.616</v>
       </c>
       <c r="N18" t="n">
         <v>77</v>
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7382</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0641</v>
+        <v>0.0521</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2882</v>
+        <v>-0.3328</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7382</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7382</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5803</v>
+        <v>0.4738</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>77</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5803</v>
+        <v>0.4738</v>
       </c>
       <c r="N19" t="n">
         <v>77</v>
@@ -1324,22 +1324,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5179</v>
+        <v>0.4321</v>
       </c>
       <c r="C20" t="n">
-        <v>0.045</v>
+        <v>0.0375</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3884</v>
+        <v>-0.4089</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5179</v>
+        <v>0.4321</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5179</v>
+        <v>0.4321</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4071</v>
+        <v>0.3416</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>85</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4071</v>
+        <v>0.3416</v>
       </c>
       <c r="N20" t="n">
         <v>85</v>
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4323</v>
+        <v>0.3597</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0376</v>
+        <v>0.0313</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4274</v>
+        <v>-0.4419</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4323</v>
+        <v>0.3597</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4323</v>
+        <v>0.3597</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3398</v>
+        <v>0.2844</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>144</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3398</v>
+        <v>0.2844</v>
       </c>
       <c r="N21" t="n">
         <v>144</v>
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2745</v>
+        <v>0.2031</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0239</v>
+        <v>0.0176</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4992</v>
+        <v>-0.5133</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2745</v>
+        <v>0.2031</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2745</v>
+        <v>0.2031</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2158</v>
+        <v>0.1606</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>128</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2158</v>
+        <v>0.1606</v>
       </c>
       <c r="N22" t="n">
         <v>128</v>
@@ -1458,26 +1458,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>reatz</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0849</v>
+        <v>0.0455</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0074</v>
+        <v>0.004</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5856</v>
+        <v>-0.5851</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0849</v>
+        <v>0.0455</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0849</v>
+        <v>0.0455</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,44 +1486,44 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0667</v>
+        <v>0.0359</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0667</v>
+        <v>0.0359</v>
       </c>
       <c r="N23" t="n">
-        <v>233</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>reatz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.081</v>
+        <v>0.0157</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007</v>
+        <v>0.0014</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5873</v>
+        <v>-0.5986</v>
       </c>
       <c r="E24" t="n">
-        <v>0.081</v>
+        <v>0.0157</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.081</v>
+        <v>0.0157</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1532,44 +1532,44 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0124</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="M24" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0124</v>
       </c>
       <c r="N24" t="n">
-        <v>77</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>solo</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0321</v>
+        <v>-0.0314</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0028</v>
+        <v>-0.0027</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6096</v>
+        <v>-0.6201</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0321</v>
+        <v>-0.0314</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0321</v>
+        <v>-0.0314</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1578,44 +1578,44 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0252</v>
+        <v>-0.0248</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0252</v>
+        <v>-0.0248</v>
       </c>
       <c r="N25" t="n">
-        <v>128</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>solo</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0262</v>
+        <v>-0.0573</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0023</v>
+        <v>-0.005</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6361</v>
+        <v>-0.6319</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0262</v>
+        <v>-0.0573</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0262</v>
+        <v>-0.0573</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1624,19 +1624,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0206</v>
+        <v>-0.0453</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0206</v>
+        <v>-0.0453</v>
       </c>
       <c r="N26" t="n">
-        <v>65</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27">
@@ -1646,22 +1646,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1043</v>
+        <v>-0.1261</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0091</v>
+        <v>-0.011</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6717</v>
+        <v>-0.6632</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1043</v>
+        <v>-0.1261</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.1043</v>
+        <v>-0.1261</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.082</v>
+        <v>-0.0997</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>65</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.082</v>
+        <v>-0.0997</v>
       </c>
       <c r="N27" t="n">
         <v>65</v>
@@ -1688,26 +1688,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>zeff</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2221</v>
+        <v>-0.128</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0193</v>
+        <v>-0.0111</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.6641</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2221</v>
+        <v>-0.128</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2221</v>
+        <v>-0.128</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1716,44 +1716,44 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1746</v>
+        <v>-0.1012</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1746</v>
+        <v>-0.1012</v>
       </c>
       <c r="N28" t="n">
-        <v>128</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>xccurate</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2231</v>
+        <v>-0.2478</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0194</v>
+        <v>-0.0215</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7258</v>
+        <v>-0.7187</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2231</v>
+        <v>-0.2478</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2231</v>
+        <v>-0.2478</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1762,44 +1762,44 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.1754</v>
+        <v>-0.1959</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1754</v>
+        <v>-0.1959</v>
       </c>
       <c r="N29" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>xccurate</t>
+          <t>zeff</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3012</v>
+        <v>-0.2509</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0262</v>
+        <v>-0.0218</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7613</v>
+        <v>-0.7201</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3012</v>
+        <v>-0.2509</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3012</v>
+        <v>-0.2509</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1808,19 +1808,19 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2368</v>
+        <v>-0.1984</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2368</v>
+        <v>-0.1984</v>
       </c>
       <c r="N30" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3131</v>
+        <v>-0.3687</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0272</v>
+        <v>-0.032</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7667</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3131</v>
+        <v>-0.3687</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.3131</v>
+        <v>-0.3687</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2461</v>
+        <v>-0.2915</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>65</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2461</v>
+        <v>-0.2915</v>
       </c>
       <c r="N31" t="n">
         <v>65</v>
@@ -1876,22 +1876,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4403</v>
+        <v>-0.4537</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0383</v>
+        <v>-0.0394</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8246</v>
+        <v>-0.8125</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4403</v>
+        <v>-0.4537</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4403</v>
+        <v>-0.4537</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.3461</v>
+        <v>-0.3587</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>65</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3461</v>
+        <v>-0.3587</v>
       </c>
       <c r="N32" t="n">
         <v>65</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.509</v>
+        <v>-0.526</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0442</v>
+        <v>-0.0457</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8559</v>
+        <v>-0.8454</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.509</v>
+        <v>-0.526</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.509</v>
+        <v>-0.526</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.4001</v>
+        <v>-0.4159</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>65</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4001</v>
+        <v>-0.4159</v>
       </c>
       <c r="N33" t="n">
         <v>65</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0512</v>
+        <v>-1.0317</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0897</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.1027</v>
+        <v>-1.0758</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0512</v>
+        <v>-1.0317</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.0512</v>
+        <v>-1.0317</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.8263</v>
+        <v>-0.8157</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>36</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8263</v>
+        <v>-0.8157</v>
       </c>
       <c r="N34" t="n">
         <v>36</v>
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0654</v>
+        <v>-1.0712</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0926</v>
+        <v>-0.0931</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1092</v>
+        <v>-1.0938</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0654</v>
+        <v>-1.0712</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.0654</v>
+        <v>-1.0712</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8375</v>
+        <v>-0.8469</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>85</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8375</v>
+        <v>-0.8469</v>
       </c>
       <c r="N35" t="n">
         <v>85</v>
@@ -2060,22 +2060,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1159</v>
+        <v>-1.1024</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.097</v>
+        <v>-0.0958</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1322</v>
+        <v>-1.108</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1159</v>
+        <v>-1.1024</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.1159</v>
+        <v>-1.1024</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8772</v>
+        <v>-0.8716</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>36</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8772</v>
+        <v>-0.8716</v>
       </c>
       <c r="N36" t="n">
         <v>36</v>
@@ -2106,22 +2106,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2317</v>
+        <v>-1.1686</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.107</v>
+        <v>-0.1016</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1849</v>
+        <v>-1.1381</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2317</v>
+        <v>-1.1686</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.2317</v>
+        <v>-1.1686</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>85</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>85</v>
@@ -2152,22 +2152,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2722</v>
+        <v>-1.2648</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1106</v>
+        <v>-0.1099</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2033</v>
+        <v>-1.182</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2722</v>
+        <v>-1.2648</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.2722</v>
+        <v>-1.2648</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2198,22 +2198,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2722</v>
+        <v>-1.2648</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1106</v>
+        <v>-0.1099</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2033</v>
+        <v>-1.182</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2722</v>
+        <v>-1.2648</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>-1.2722</v>
+        <v>-1.2648</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3195</v>
+        <v>-1.3458</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1147</v>
+        <v>-0.117</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2249</v>
+        <v>-1.2189</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3195</v>
+        <v>-1.3458</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.3195</v>
+        <v>-1.3458</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.0372</v>
+        <v>-1.064</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>128</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.0372</v>
+        <v>-1.064</v>
       </c>
       <c r="N40" t="n">
         <v>128</v>
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4947</v>
+        <v>-1.4132</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1299</v>
+        <v>-0.1228</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3046</v>
+        <v>-1.2496</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4947</v>
+        <v>-1.4132</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.4947</v>
+        <v>-1.4132</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.1749</v>
+        <v>-1.1173</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>144</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.1749</v>
+        <v>-1.1173</v>
       </c>
       <c r="N41" t="n">
         <v>144</v>
@@ -2429,10 +2429,10 @@
         <v>0.7</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3022</v>
+        <v>-0.2911</v>
       </c>
       <c r="J2" t="n">
-        <v>-6.6484</v>
+        <v>-6.4042</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.312</v>
+        <v>-0.3013</v>
       </c>
       <c r="J3" t="n">
-        <v>-6.864</v>
+        <v>-6.6286</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.63</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3678</v>
+        <v>-0.3594</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.0916</v>
+        <v>-7.9068</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4271</v>
+        <v>-0.4203</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.3962</v>
+        <v>-9.246600000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.4</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5677</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.4894</v>
+        <v>-12.6302</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.65</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3378</v>
+        <v>1.374</v>
       </c>
       <c r="J7" t="n">
-        <v>29.4316</v>
+        <v>30.228</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.62</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2875</v>
+        <v>1.3193</v>
       </c>
       <c r="J8" t="n">
-        <v>28.325</v>
+        <v>29.0246</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2538</v>
+        <v>1.2819</v>
       </c>
       <c r="J9" t="n">
-        <v>27.5836</v>
+        <v>28.2018</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.49</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0672</v>
+        <v>1.0767</v>
       </c>
       <c r="J10" t="n">
-        <v>23.4784</v>
+        <v>23.6874</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2905</v>
+        <v>0.2568</v>
       </c>
       <c r="J11" t="n">
-        <v>6.391</v>
+        <v>5.6496</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.34</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6513</v>
+        <v>0.5926</v>
       </c>
       <c r="J12" t="n">
-        <v>19.539</v>
+        <v>17.778</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.16</v>
       </c>
       <c r="I13" t="n">
-        <v>0.358</v>
+        <v>0.304</v>
       </c>
       <c r="J13" t="n">
-        <v>10.74</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0515</v>
       </c>
       <c r="J14" t="n">
-        <v>2.13</v>
+        <v>1.545</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.9</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1495</v>
+        <v>-0.1296</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.485</v>
+        <v>-3.888</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.73</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3225</v>
+        <v>-0.3061</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.675000000000001</v>
+        <v>-9.183</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.19</v>
       </c>
       <c r="I17" t="n">
-        <v>0.546</v>
+        <v>0.506</v>
       </c>
       <c r="J17" t="n">
-        <v>16.38</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.19</v>
       </c>
       <c r="I18" t="n">
-        <v>0.546</v>
+        <v>0.506</v>
       </c>
       <c r="J18" t="n">
-        <v>16.38</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.17</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4998</v>
+        <v>0.4589</v>
       </c>
       <c r="J19" t="n">
-        <v>14.994</v>
+        <v>13.767</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.05</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1912</v>
+        <v>0.1607</v>
       </c>
       <c r="J20" t="n">
-        <v>5.736</v>
+        <v>4.821</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.73</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7575</v>
+        <v>-0.7298</v>
       </c>
       <c r="J21" t="n">
-        <v>-22.725</v>
+        <v>-21.894</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.77</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2088</v>
+        <v>-0.1882</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.5496</v>
+        <v>-3.1994</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.74</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2417</v>
+        <v>-0.2244</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.1089</v>
+        <v>-3.8148</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.67</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3147</v>
+        <v>-0.3043</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.3499</v>
+        <v>-5.1731</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.25</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6922</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.7674</v>
+        <v>-12.2281</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.21</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7285</v>
+        <v>-0.7635999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.3845</v>
+        <v>-12.9812</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>2.63</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J27" t="n">
-        <v>31.3701</v>
+        <v>33.6974</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.68</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3663</v>
+        <v>1.4103</v>
       </c>
       <c r="J28" t="n">
-        <v>23.2271</v>
+        <v>23.9751</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.49</v>
       </c>
       <c r="I29" t="n">
-        <v>1.0499</v>
+        <v>1.0641</v>
       </c>
       <c r="J29" t="n">
-        <v>17.8483</v>
+        <v>18.0897</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.31</v>
       </c>
       <c r="I30" t="n">
-        <v>0.713</v>
+        <v>0.6966</v>
       </c>
       <c r="J30" t="n">
-        <v>12.121</v>
+        <v>11.8422</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.16</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3914</v>
+        <v>0.3565</v>
       </c>
       <c r="J31" t="n">
-        <v>6.6538</v>
+        <v>6.0605</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.05</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1836</v>
+        <v>0.1464</v>
       </c>
       <c r="J32" t="n">
-        <v>4.59</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0742</v>
+        <v>0.0549</v>
       </c>
       <c r="J33" t="n">
-        <v>1.855</v>
+        <v>1.3725</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.85</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1883</v>
+        <v>-0.1705</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.7075</v>
+        <v>-4.2625</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.74</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2947</v>
+        <v>-0.2768</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.3675</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.55</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4663</v>
+        <v>-0.4616</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.6575</v>
+        <v>-11.54</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7532</v>
+        <v>0.7391</v>
       </c>
       <c r="J37" t="n">
-        <v>18.83</v>
+        <v>18.4775</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.35</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7388</v>
+        <v>0.725</v>
       </c>
       <c r="J38" t="n">
-        <v>18.47</v>
+        <v>18.125</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.29</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6511</v>
+        <v>0.6402</v>
       </c>
       <c r="J39" t="n">
-        <v>16.2775</v>
+        <v>16.005</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.22</v>
       </c>
       <c r="I40" t="n">
-        <v>0.546</v>
+        <v>0.5402</v>
       </c>
       <c r="J40" t="n">
-        <v>13.65</v>
+        <v>13.505</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.98</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1418</v>
+        <v>-0.115</v>
       </c>
       <c r="J41" t="n">
-        <v>-3.545</v>
+        <v>-2.875</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.26</v>
       </c>
       <c r="I42" t="n">
-        <v>0.528</v>
+        <v>0.501</v>
       </c>
       <c r="J42" t="n">
-        <v>13.728</v>
+        <v>13.026</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.09</v>
       </c>
       <c r="I43" t="n">
-        <v>0.251</v>
+        <v>0.2045</v>
       </c>
       <c r="J43" t="n">
-        <v>6.526</v>
+        <v>5.317</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.92</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1176</v>
+        <v>-0.1011</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.0576</v>
+        <v>-2.6286</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.87</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1727</v>
+        <v>-0.1534</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.4902</v>
+        <v>-3.9884</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.43</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5753</v>
+        <v>-0.5871</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.9578</v>
+        <v>-15.2646</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.46</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8988</v>
+        <v>0.8838</v>
       </c>
       <c r="J47" t="n">
-        <v>23.3688</v>
+        <v>22.9788</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7281</v>
+        <v>0.7138</v>
       </c>
       <c r="J48" t="n">
-        <v>18.9306</v>
+        <v>18.5588</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.27</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6241</v>
+        <v>0.6135</v>
       </c>
       <c r="J49" t="n">
-        <v>16.2266</v>
+        <v>15.951</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.02</v>
       </c>
       <c r="I50" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0491</v>
       </c>
       <c r="J50" t="n">
-        <v>1.6952</v>
+        <v>1.2766</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.98</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1373</v>
+        <v>-0.1103</v>
       </c>
       <c r="J51" t="n">
-        <v>-3.5698</v>
+        <v>-2.8678</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.48</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9396</v>
+        <v>0.9255</v>
       </c>
       <c r="J52" t="n">
-        <v>28.188</v>
+        <v>27.765</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.25</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6012</v>
+        <v>0.5899</v>
       </c>
       <c r="J53" t="n">
-        <v>18.036</v>
+        <v>17.697</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.24</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5855</v>
+        <v>0.575</v>
       </c>
       <c r="J54" t="n">
-        <v>17.565</v>
+        <v>17.25</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.12</v>
       </c>
       <c r="I55" t="n">
-        <v>0.368</v>
+        <v>0.3322</v>
       </c>
       <c r="J55" t="n">
-        <v>11.04</v>
+        <v>9.965999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.68</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8797</v>
+        <v>-0.8661</v>
       </c>
       <c r="J56" t="n">
-        <v>-26.391</v>
+        <v>-25.983</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.31</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5652</v>
+        <v>0.539</v>
       </c>
       <c r="J57" t="n">
-        <v>16.956</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.22</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4573</v>
+        <v>0.4062</v>
       </c>
       <c r="J58" t="n">
-        <v>13.719</v>
+        <v>12.186</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.02</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0722</v>
+        <v>0.0519</v>
       </c>
       <c r="J59" t="n">
-        <v>2.166</v>
+        <v>1.557</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2535</v>
+        <v>-0.2337</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.605</v>
+        <v>-7.011</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.71</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3395</v>
+        <v>-0.3242</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.185</v>
+        <v>-9.726000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.13</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2915</v>
+        <v>0.2863</v>
       </c>
       <c r="J62" t="n">
-        <v>7.2875</v>
+        <v>7.1575</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.75</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2804</v>
+        <v>-0.2631</v>
       </c>
       <c r="J63" t="n">
-        <v>-7.01</v>
+        <v>-6.5775</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.73</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.299</v>
+        <v>-0.2821</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.475</v>
+        <v>-7.0525</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.68</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.345</v>
+        <v>-0.3298</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.625</v>
+        <v>-8.244999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.67</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3541</v>
+        <v>-0.3394</v>
       </c>
       <c r="J66" t="n">
-        <v>-8.852499999999999</v>
+        <v>-8.484999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6905</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>17.2625</v>
+        <v>16.1425</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.56</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6118</v>
+        <v>0.5735</v>
       </c>
       <c r="J68" t="n">
-        <v>15.295</v>
+        <v>14.3375</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.27</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3741</v>
+        <v>0.3164</v>
       </c>
       <c r="J69" t="n">
-        <v>9.352499999999999</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.0204</v>
+        <v>-0.0181</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.51</v>
+        <v>-0.4525</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.91</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1577</v>
+        <v>-0.1393</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.9425</v>
+        <v>-3.4825</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.52</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9932</v>
+        <v>0.9808</v>
       </c>
       <c r="J72" t="n">
-        <v>23.8368</v>
+        <v>23.5392</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8387</v>
+        <v>0.8228</v>
       </c>
       <c r="J73" t="n">
-        <v>20.1288</v>
+        <v>19.7472</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.13</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3912</v>
+        <v>0.3554</v>
       </c>
       <c r="J74" t="n">
-        <v>9.3888</v>
+        <v>8.5296</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.88</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4256</v>
+        <v>-0.3838</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.2144</v>
+        <v>-9.2112</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.87</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.451</v>
+        <v>-0.4095</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.824</v>
+        <v>-9.827999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.23</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4662</v>
+        <v>0.4174</v>
       </c>
       <c r="J77" t="n">
-        <v>11.1888</v>
+        <v>10.0176</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.17</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3748</v>
+        <v>0.3199</v>
       </c>
       <c r="J78" t="n">
-        <v>8.995200000000001</v>
+        <v>7.6776</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.01</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0405</v>
+        <v>0.0281</v>
       </c>
       <c r="J79" t="n">
-        <v>0.972</v>
+        <v>0.6744</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1612</v>
+        <v>-0.1409</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.8688</v>
+        <v>-3.3816</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.87</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1832</v>
+        <v>-0.1626</v>
       </c>
       <c r="J81" t="n">
-        <v>-4.3968</v>
+        <v>-3.9024</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.96</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4737</v>
+        <v>1.4889</v>
       </c>
       <c r="J82" t="n">
-        <v>28.0003</v>
+        <v>28.2891</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.88</v>
       </c>
       <c r="I83" t="n">
-        <v>1.3799</v>
+        <v>1.3879</v>
       </c>
       <c r="J83" t="n">
-        <v>26.2181</v>
+        <v>26.3701</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.75</v>
       </c>
       <c r="I84" t="n">
-        <v>1.2246</v>
+        <v>1.2236</v>
       </c>
       <c r="J84" t="n">
-        <v>23.2674</v>
+        <v>23.2484</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.5333</v>
+        <v>-1.5409</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.93</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3432</v>
+        <v>-0.3123</v>
       </c>
       <c r="J86" t="n">
-        <v>-6.5208</v>
+        <v>-5.9337</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.96</v>
       </c>
       <c r="I87" t="n">
-        <v>0.0132</v>
+        <v>0.0564</v>
       </c>
       <c r="J87" t="n">
-        <v>0.2508</v>
+        <v>1.0716</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.58</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.409</v>
+        <v>-0.4021</v>
       </c>
       <c r="J88" t="n">
-        <v>-7.771</v>
+        <v>-7.6399</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.54</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.443</v>
+        <v>-0.4373</v>
       </c>
       <c r="J89" t="n">
-        <v>-8.417</v>
+        <v>-8.3087</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.47</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5043</v>
+        <v>-0.5031</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.5817</v>
+        <v>-9.5589</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.38</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5839</v>
+        <v>-0.5926</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.0941</v>
+        <v>-11.2594</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>2.12</v>
       </c>
       <c r="I92" t="n">
-        <v>1.624</v>
+        <v>1.6528</v>
       </c>
       <c r="J92" t="n">
-        <v>27.608</v>
+        <v>28.0976</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.88</v>
       </c>
       <c r="I93" t="n">
-        <v>1.3542</v>
+        <v>1.3635</v>
       </c>
       <c r="J93" t="n">
-        <v>23.0214</v>
+        <v>23.1795</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.57</v>
       </c>
       <c r="I94" t="n">
-        <v>0.9902</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="J94" t="n">
-        <v>16.8334</v>
+        <v>16.8028</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.5</v>
       </c>
       <c r="I95" t="n">
-        <v>0.9008</v>
+        <v>0.8979</v>
       </c>
       <c r="J95" t="n">
-        <v>15.3136</v>
+        <v>15.2643</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.36</v>
       </c>
       <c r="I96" t="n">
-        <v>0.7108</v>
+        <v>0.7071</v>
       </c>
       <c r="J96" t="n">
-        <v>12.0836</v>
+        <v>12.0207</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>0.76</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.1886</v>
+        <v>-0.1576</v>
       </c>
       <c r="J97" t="n">
-        <v>-3.2062</v>
+        <v>-2.6792</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.58</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.3833</v>
+        <v>-0.3784</v>
       </c>
       <c r="J98" t="n">
-        <v>-6.5161</v>
+        <v>-6.4328</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.49</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.4682</v>
+        <v>-0.4695</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.9594</v>
+        <v>-7.9815</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.24</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.6915</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="J100" t="n">
-        <v>-11.7555</v>
+        <v>-12.1924</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.23</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7009</v>
+        <v>-0.7286</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.9153</v>
+        <v>-12.3862</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.3</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5416</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="J102" t="n">
-        <v>15.7064</v>
+        <v>14.8944</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.23</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4593</v>
+        <v>0.4089</v>
       </c>
       <c r="J103" t="n">
-        <v>13.3197</v>
+        <v>11.8581</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.01</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0353</v>
+        <v>0.0247</v>
       </c>
       <c r="J104" t="n">
-        <v>1.0237</v>
+        <v>0.7163</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.99</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0307</v>
+        <v>-0.022</v>
       </c>
       <c r="J105" t="n">
-        <v>-0.8903</v>
+        <v>-0.638</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.86</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1977</v>
+        <v>-0.1771</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.7333</v>
+        <v>-5.1359</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.2</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5403</v>
+        <v>0.5283</v>
       </c>
       <c r="J107" t="n">
-        <v>15.6687</v>
+        <v>15.3207</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.17</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4888</v>
+        <v>0.465</v>
       </c>
       <c r="J108" t="n">
-        <v>14.1752</v>
+        <v>13.485</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.05</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1941</v>
+        <v>0.1619</v>
       </c>
       <c r="J109" t="n">
-        <v>5.6289</v>
+        <v>4.6951</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.02</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0951</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="J110" t="n">
-        <v>2.7579</v>
+        <v>2.1576</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.75</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.6761</v>
       </c>
       <c r="J111" t="n">
-        <v>-20.5378</v>
+        <v>-19.6069</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.88</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8087</v>
+        <v>0.7563</v>
       </c>
       <c r="J112" t="n">
-        <v>16.9827</v>
+        <v>15.8823</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.84</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7827</v>
+        <v>0.7319</v>
       </c>
       <c r="J113" t="n">
-        <v>16.4367</v>
+        <v>15.3699</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.52</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5675</v>
+        <v>0.5357</v>
       </c>
       <c r="J114" t="n">
-        <v>11.9175</v>
+        <v>11.2497</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.28</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3691</v>
+        <v>0.315</v>
       </c>
       <c r="J115" t="n">
-        <v>7.7511</v>
+        <v>6.615</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.99</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.0602</v>
+        <v>-0.0533</v>
       </c>
       <c r="J116" t="n">
-        <v>-1.2642</v>
+        <v>-1.1193</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4347</v>
+        <v>0.4711</v>
       </c>
       <c r="J117" t="n">
-        <v>9.1287</v>
+        <v>9.8931</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.78</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.2375</v>
+        <v>-0.2231</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.9875</v>
+        <v>-4.6851</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.58</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4196</v>
+        <v>-0.4105</v>
       </c>
       <c r="J119" t="n">
-        <v>-8.8116</v>
+        <v>-8.6205</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.42</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5601</v>
+        <v>-0.5661</v>
       </c>
       <c r="J120" t="n">
-        <v>-11.7621</v>
+        <v>-11.8881</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.38</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5949</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.4929</v>
+        <v>-12.7344</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.44</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7229</v>
+        <v>0.6915</v>
       </c>
       <c r="J122" t="n">
-        <v>19.5183</v>
+        <v>18.6705</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.06</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1759</v>
+        <v>0.1374</v>
       </c>
       <c r="J123" t="n">
-        <v>4.7493</v>
+        <v>3.7098</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.91</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1326</v>
+        <v>-0.114</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.5802</v>
+        <v>-3.078</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.71</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3354</v>
+        <v>-0.3194</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.0558</v>
+        <v>-8.623799999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.71</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3354</v>
+        <v>-0.3194</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.0558</v>
+        <v>-8.623799999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.65</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1601</v>
+        <v>1.1556</v>
       </c>
       <c r="J127" t="n">
-        <v>31.3227</v>
+        <v>31.2012</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.17</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4694</v>
+        <v>0.4454</v>
       </c>
       <c r="J128" t="n">
-        <v>12.6738</v>
+        <v>12.0258</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.08</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2577</v>
+        <v>0.2266</v>
       </c>
       <c r="J129" t="n">
-        <v>6.9579</v>
+        <v>6.1182</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.04</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1388</v>
+        <v>0.1151</v>
       </c>
       <c r="J130" t="n">
-        <v>3.7476</v>
+        <v>3.1077</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.03</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1052</v>
+        <v>0.0847</v>
       </c>
       <c r="J131" t="n">
-        <v>2.8404</v>
+        <v>2.2869</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.92</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.1052</v>
+        <v>-0.0911</v>
       </c>
       <c r="J132" t="n">
-        <v>-2.5248</v>
+        <v>-2.1864</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.9</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1293</v>
+        <v>-0.1142</v>
       </c>
       <c r="J133" t="n">
-        <v>-3.1032</v>
+        <v>-2.7408</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2249</v>
+        <v>-0.2076</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.3976</v>
+        <v>-4.9824</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.7</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3276</v>
+        <v>-0.3115</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.8624</v>
+        <v>-7.476</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.67</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.355</v>
+        <v>-0.3403</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.52</v>
+        <v>-8.167199999999999</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.95</v>
       </c>
       <c r="I137" t="n">
-        <v>1.5022</v>
+        <v>1.5227</v>
       </c>
       <c r="J137" t="n">
-        <v>36.0528</v>
+        <v>36.5448</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.94</v>
       </c>
       <c r="I138" t="n">
-        <v>1.4902</v>
+        <v>1.5094</v>
       </c>
       <c r="J138" t="n">
-        <v>35.7648</v>
+        <v>36.2256</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.1</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2898</v>
+        <v>0.2582</v>
       </c>
       <c r="J139" t="n">
-        <v>6.9552</v>
+        <v>6.1968</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.5274</v>
+        <v>-0.4924</v>
       </c>
       <c r="J140" t="n">
-        <v>-12.6576</v>
+        <v>-11.8176</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.79</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6676</v>
+        <v>-0.6401</v>
       </c>
       <c r="J141" t="n">
-        <v>-16.0224</v>
+        <v>-15.3624</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.47</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5483</v>
+        <v>0.5122</v>
       </c>
       <c r="J142" t="n">
-        <v>12.6109</v>
+        <v>11.7806</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.4</v>
       </c>
       <c r="I143" t="n">
-        <v>0.495</v>
+        <v>0.447</v>
       </c>
       <c r="J143" t="n">
-        <v>11.385</v>
+        <v>10.281</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.15</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2336</v>
+        <v>0.1896</v>
       </c>
       <c r="J144" t="n">
-        <v>5.3728</v>
+        <v>4.3608</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.14</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2205</v>
+        <v>0.1781</v>
       </c>
       <c r="J145" t="n">
-        <v>5.0715</v>
+        <v>4.0963</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.1</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1655</v>
+        <v>0.1303</v>
       </c>
       <c r="J146" t="n">
-        <v>3.8065</v>
+        <v>2.9969</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.92</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.1095</v>
+        <v>-0.095</v>
       </c>
       <c r="J147" t="n">
-        <v>-2.5185</v>
+        <v>-2.185</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.92</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1095</v>
+        <v>-0.095</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.5185</v>
+        <v>-2.185</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.91</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1215</v>
+        <v>-0.1065</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.7945</v>
+        <v>-2.4495</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.78</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2557</v>
+        <v>-0.2373</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.8811</v>
+        <v>-5.4579</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.62</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4034</v>
+        <v>-0.3922</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.2782</v>
+        <v>-9.0206</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.92</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.0809</v>
+        <v>-0.064</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.4562</v>
+        <v>-1.152</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.77</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2494</v>
+        <v>-0.2352</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.4892</v>
+        <v>-4.2336</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.74</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2787</v>
+        <v>-0.2652</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.0166</v>
+        <v>-4.7736</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.67</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3417</v>
+        <v>-0.3292</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.1506</v>
+        <v>-5.9256</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.3</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6651</v>
+        <v>-0.6895</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.9718</v>
+        <v>-12.411</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.71</v>
       </c>
       <c r="I157" t="n">
-        <v>1.186</v>
+        <v>1.1822</v>
       </c>
       <c r="J157" t="n">
-        <v>21.348</v>
+        <v>21.2796</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.66</v>
       </c>
       <c r="I158" t="n">
-        <v>1.1239</v>
+        <v>1.1176</v>
       </c>
       <c r="J158" t="n">
-        <v>20.2302</v>
+        <v>20.1168</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.39</v>
       </c>
       <c r="I159" t="n">
-        <v>0.7763</v>
+        <v>0.7681</v>
       </c>
       <c r="J159" t="n">
-        <v>13.9734</v>
+        <v>13.8258</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.35</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7207</v>
+        <v>0.7138</v>
       </c>
       <c r="J160" t="n">
-        <v>12.9726</v>
+        <v>12.8484</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.07</v>
       </c>
       <c r="I161" t="n">
-        <v>0.191</v>
+        <v>0.16</v>
       </c>
       <c r="J161" t="n">
-        <v>3.438</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.37</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4978</v>
+        <v>0.4506</v>
       </c>
       <c r="J162" t="n">
-        <v>14.934</v>
+        <v>13.518</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.16</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2666</v>
+        <v>0.2142</v>
       </c>
       <c r="J163" t="n">
-        <v>7.998</v>
+        <v>6.426</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.98</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0445</v>
+        <v>-0.0336</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.335</v>
+        <v>-1.008</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.89</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1605</v>
+        <v>-0.1403</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.815</v>
+        <v>-4.209</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.73</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3221</v>
+        <v>-0.3057</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.663</v>
+        <v>-9.170999999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.63</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7287</v>
+        <v>0.778</v>
       </c>
       <c r="J167" t="n">
-        <v>21.861</v>
+        <v>23.34</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.18</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3039</v>
+        <v>0.2925</v>
       </c>
       <c r="J168" t="n">
-        <v>9.117000000000001</v>
+        <v>8.775</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.16</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2768</v>
+        <v>0.2638</v>
       </c>
       <c r="J169" t="n">
-        <v>8.304</v>
+        <v>7.914</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.72</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.334</v>
+        <v>-0.3187</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.02</v>
+        <v>-9.561</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.59</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4503</v>
+        <v>-0.4462</v>
       </c>
       <c r="J171" t="n">
-        <v>-13.509</v>
+        <v>-13.386</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.04</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1282</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J172" t="n">
-        <v>3.846</v>
+        <v>2.901</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.04</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1282</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J173" t="n">
-        <v>3.846</v>
+        <v>2.901</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>0.0022</v>
+        <v>0.001</v>
       </c>
       <c r="J174" t="n">
-        <v>0.066</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.95</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0843</v>
+        <v>-0.0692</v>
       </c>
       <c r="J175" t="n">
-        <v>-2.529</v>
+        <v>-2.076</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.85</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.1993</v>
+        <v>-0.1788</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.979</v>
+        <v>-5.364</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.45</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8952</v>
+        <v>0.88</v>
       </c>
       <c r="J177" t="n">
-        <v>26.856</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.38</v>
       </c>
       <c r="I178" t="n">
-        <v>0.795</v>
+        <v>0.7791</v>
       </c>
       <c r="J178" t="n">
-        <v>23.85</v>
+        <v>23.373</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.06</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2058</v>
+        <v>0.177</v>
       </c>
       <c r="J179" t="n">
-        <v>6.174</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2058</v>
+        <v>0.177</v>
       </c>
       <c r="J180" t="n">
-        <v>6.174</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.87</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4513</v>
+        <v>-0.4099</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.539</v>
+        <v>-12.297</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.15</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4321</v>
+        <v>0.3931</v>
       </c>
       <c r="J182" t="n">
-        <v>10.8025</v>
+        <v>9.827500000000001</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.91</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.108</v>
+        <v>-0.0931</v>
       </c>
       <c r="J183" t="n">
-        <v>-2.7</v>
+        <v>-2.3275</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2189</v>
+        <v>-0.2033</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.4725</v>
+        <v>-5.0825</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4468</v>
+        <v>-0.4394</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.17</v>
+        <v>-10.985</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.29</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6792</v>
+        <v>-0.7076</v>
       </c>
       <c r="J186" t="n">
-        <v>-16.98</v>
+        <v>-17.69</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.77</v>
       </c>
       <c r="I187" t="n">
-        <v>1.282</v>
+        <v>1.2834</v>
       </c>
       <c r="J187" t="n">
-        <v>32.05</v>
+        <v>32.085</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.36</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7432</v>
+        <v>0.732</v>
       </c>
       <c r="J188" t="n">
-        <v>18.58</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.21</v>
       </c>
       <c r="I189" t="n">
-        <v>0.5216</v>
+        <v>0.5169</v>
       </c>
       <c r="J189" t="n">
-        <v>13.04</v>
+        <v>12.9225</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5054</v>
+        <v>0.4975</v>
       </c>
       <c r="J190" t="n">
-        <v>12.635</v>
+        <v>12.4375</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>1.08</v>
       </c>
       <c r="I191" t="n">
-        <v>0.2363</v>
+        <v>0.2059</v>
       </c>
       <c r="J191" t="n">
-        <v>5.9075</v>
+        <v>5.1475</v>
       </c>
     </row>
   </sheetData>
